--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_diversified.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_diversified.xlsx
@@ -1382,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1519,22 +1519,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2491350123090307</v>
+        <v>0.2487488327881053</v>
       </c>
       <c r="C2">
-        <v>595.3978056876</v>
+        <v>591.9416481009172</v>
       </c>
       <c r="D2">
-        <v>575.8978056876</v>
+        <v>576.9936481009172</v>
       </c>
       <c r="E2">
-        <v>-263.9</v>
+        <v>-259.348</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.552</v>
       </c>
       <c r="G2">
         <v>19.5</v>
@@ -1555,28 +1555,28 @@
         <v>50.375</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2289656</v>
       </c>
       <c r="N2">
-        <v>50.375</v>
+        <v>50.1460344</v>
       </c>
       <c r="O2">
-        <v>8.563750000000001</v>
+        <v>8.524825848000001</v>
       </c>
       <c r="P2">
-        <v>41.81125</v>
+        <v>41.621208552</v>
       </c>
       <c r="Q2">
-        <v>42.81125</v>
+        <v>42.621208552</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2491350123090307</v>
+        <v>0.2508397401900054</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7343128976927311</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>220.0112156585968</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1601,22 +1601,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2487488327881053</v>
+        <v>0.24836265326718</v>
       </c>
       <c r="C3">
-        <v>591.9416481009172</v>
+        <v>588.4896688945164</v>
       </c>
       <c r="D3">
-        <v>576.9936481009172</v>
+        <v>578.0936688945164</v>
       </c>
       <c r="E3">
-        <v>-259.348</v>
+        <v>-254.796</v>
       </c>
       <c r="F3">
-        <v>4.552</v>
+        <v>9.103999999999999</v>
       </c>
       <c r="G3">
         <v>19.5</v>
@@ -1637,28 +1637,28 @@
         <v>50.375</v>
       </c>
       <c r="M3">
-        <v>0.2289656</v>
+        <v>0.4579311999999999</v>
       </c>
       <c r="N3">
-        <v>50.1460344</v>
+        <v>49.9170688</v>
       </c>
       <c r="O3">
-        <v>8.524825848000001</v>
+        <v>8.485901696000001</v>
       </c>
       <c r="P3">
-        <v>41.621208552</v>
+        <v>41.431167104</v>
       </c>
       <c r="Q3">
-        <v>42.621208552</v>
+        <v>42.431167104</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2508397401900054</v>
+        <v>0.252579258435898</v>
       </c>
       <c r="T3">
-        <v>0.7343128976927311</v>
+        <v>0.7405426689680316</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>220.0112156585968</v>
+        <v>110.0056078292984</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1683,22 +1683,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.24836265326718</v>
+        <v>0.2479764737462546</v>
       </c>
       <c r="C4">
-        <v>588.4896688945164</v>
+        <v>585.0418920119099</v>
       </c>
       <c r="D4">
-        <v>578.0936688945164</v>
+        <v>579.1978920119099</v>
       </c>
       <c r="E4">
-        <v>-254.796</v>
+        <v>-250.244</v>
       </c>
       <c r="F4">
-        <v>9.103999999999999</v>
+        <v>13.656</v>
       </c>
       <c r="G4">
         <v>19.5</v>
@@ -1719,28 +1719,28 @@
         <v>50.375</v>
       </c>
       <c r="M4">
-        <v>0.4579311999999999</v>
+        <v>0.6868967999999999</v>
       </c>
       <c r="N4">
-        <v>49.9170688</v>
+        <v>49.6881032</v>
       </c>
       <c r="O4">
-        <v>8.485901696000001</v>
+        <v>8.446977544000001</v>
       </c>
       <c r="P4">
-        <v>41.431167104</v>
+        <v>41.241125656</v>
       </c>
       <c r="Q4">
-        <v>42.431167104</v>
+        <v>42.241125656</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.252579258435898</v>
+        <v>0.2543546430373759</v>
       </c>
       <c r="T4">
-        <v>0.7405426689680316</v>
+        <v>0.746900889135606</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>110.0056078292984</v>
+        <v>73.33707188619893</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1765,22 +1765,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2479764737462546</v>
+        <v>0.2475902942253292</v>
       </c>
       <c r="C5">
-        <v>585.0418920119099</v>
+        <v>581.5983415798975</v>
       </c>
       <c r="D5">
-        <v>579.1978920119099</v>
+        <v>580.3063415798974</v>
       </c>
       <c r="E5">
-        <v>-250.244</v>
+        <v>-245.692</v>
       </c>
       <c r="F5">
-        <v>13.656</v>
+        <v>18.208</v>
       </c>
       <c r="G5">
         <v>19.5</v>
@@ -1801,28 +1801,28 @@
         <v>50.375</v>
       </c>
       <c r="M5">
-        <v>0.6868967999999999</v>
+        <v>0.9158623999999999</v>
       </c>
       <c r="N5">
-        <v>49.6881032</v>
+        <v>49.4591376</v>
       </c>
       <c r="O5">
-        <v>8.446977544000001</v>
+        <v>8.408053392000001</v>
       </c>
       <c r="P5">
-        <v>41.241125656</v>
+        <v>41.051084208</v>
       </c>
       <c r="Q5">
-        <v>42.241125656</v>
+        <v>42.051084208</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2543546430373759</v>
+        <v>0.2561670148180513</v>
       </c>
       <c r="T5">
-        <v>0.746900889135606</v>
+        <v>0.7533915722233384</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.33707188619893</v>
+        <v>55.00280391464919</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2475902942253292</v>
+        <v>0.2472041147044039</v>
       </c>
       <c r="C6">
-        <v>581.5983415798975</v>
+        <v>578.159041910326</v>
       </c>
       <c r="D6">
-        <v>580.3063415798974</v>
+        <v>581.419041910326</v>
       </c>
       <c r="E6">
-        <v>-245.692</v>
+        <v>-241.14</v>
       </c>
       <c r="F6">
-        <v>18.208</v>
+        <v>22.76</v>
       </c>
       <c r="G6">
         <v>19.5</v>
@@ -1883,28 +1883,28 @@
         <v>50.375</v>
       </c>
       <c r="M6">
-        <v>0.9158623999999999</v>
+        <v>1.144828</v>
       </c>
       <c r="N6">
-        <v>49.4591376</v>
+        <v>49.230172</v>
       </c>
       <c r="O6">
-        <v>8.408053392000001</v>
+        <v>8.369129240000001</v>
       </c>
       <c r="P6">
-        <v>41.051084208</v>
+        <v>40.86104276</v>
       </c>
       <c r="Q6">
-        <v>42.051084208</v>
+        <v>41.86104276</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2561670148180513</v>
+        <v>0.2580175417941094</v>
       </c>
       <c r="T6">
-        <v>0.7533915722233384</v>
+        <v>0.7600189012708124</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.00280391464919</v>
+        <v>44.00224313171935</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1929,22 +1929,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2472041147044039</v>
+        <v>0.2468179351834786</v>
       </c>
       <c r="C7">
-        <v>578.159041910326</v>
+        <v>574.7240175018663</v>
       </c>
       <c r="D7">
-        <v>581.419041910326</v>
+        <v>582.5360175018664</v>
       </c>
       <c r="E7">
-        <v>-241.14</v>
+        <v>-236.588</v>
       </c>
       <c r="F7">
-        <v>22.76</v>
+        <v>27.312</v>
       </c>
       <c r="G7">
         <v>19.5</v>
@@ -1965,28 +1965,28 @@
         <v>50.375</v>
       </c>
       <c r="M7">
-        <v>1.144828</v>
+        <v>1.3737936</v>
       </c>
       <c r="N7">
-        <v>49.230172</v>
+        <v>49.0012064</v>
       </c>
       <c r="O7">
-        <v>8.369129240000001</v>
+        <v>8.330205088000001</v>
       </c>
       <c r="P7">
-        <v>40.86104276</v>
+        <v>40.671001312</v>
       </c>
       <c r="Q7">
-        <v>41.86104276</v>
+        <v>41.671001312</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2580175417941094</v>
+        <v>0.2599074416845517</v>
       </c>
       <c r="T7">
-        <v>0.7600189012708124</v>
+        <v>0.7667872373192967</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.00224313171935</v>
+        <v>36.66853594309946</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2011,22 +2011,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2468179351834786</v>
+        <v>0.2464317556625532</v>
       </c>
       <c r="C8">
-        <v>574.7240175018663</v>
+        <v>571.2932930418114</v>
       </c>
       <c r="D8">
-        <v>582.5360175018664</v>
+        <v>583.6572930418114</v>
       </c>
       <c r="E8">
-        <v>-236.588</v>
+        <v>-232.036</v>
       </c>
       <c r="F8">
-        <v>27.312</v>
+        <v>31.864</v>
       </c>
       <c r="G8">
         <v>19.5</v>
@@ -2047,28 +2047,28 @@
         <v>50.375</v>
       </c>
       <c r="M8">
-        <v>1.3737936</v>
+        <v>1.6027592</v>
       </c>
       <c r="N8">
-        <v>49.0012064</v>
+        <v>48.7722408</v>
       </c>
       <c r="O8">
-        <v>8.330205088000001</v>
+        <v>8.291280936</v>
       </c>
       <c r="P8">
-        <v>40.671001312</v>
+        <v>40.480959864</v>
       </c>
       <c r="Q8">
-        <v>41.671001312</v>
+        <v>41.480959864</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2599074416845517</v>
+        <v>0.2618379845833905</v>
       </c>
       <c r="T8">
-        <v>0.7667872373192967</v>
+        <v>0.7737011289817267</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.66853594309946</v>
+        <v>31.43017366551383</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2093,22 +2093,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2464317556625532</v>
+        <v>0.2460455761416278</v>
       </c>
       <c r="C9">
-        <v>571.2932930418114</v>
+        <v>567.8668934078942</v>
       </c>
       <c r="D9">
-        <v>583.6572930418114</v>
+        <v>584.7828934078941</v>
       </c>
       <c r="E9">
-        <v>-232.036</v>
+        <v>-227.484</v>
       </c>
       <c r="F9">
-        <v>31.864</v>
+        <v>36.416</v>
       </c>
       <c r="G9">
         <v>19.5</v>
@@ -2129,28 +2129,28 @@
         <v>50.375</v>
       </c>
       <c r="M9">
-        <v>1.6027592</v>
+        <v>1.8317248</v>
       </c>
       <c r="N9">
-        <v>48.7722408</v>
+        <v>48.5432752</v>
       </c>
       <c r="O9">
-        <v>8.291280936</v>
+        <v>8.252356784000002</v>
       </c>
       <c r="P9">
-        <v>40.480959864</v>
+        <v>40.290918416</v>
       </c>
       <c r="Q9">
-        <v>41.480959864</v>
+        <v>41.290918416</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2618379845833905</v>
+        <v>0.2638104958061172</v>
       </c>
       <c r="T9">
-        <v>0.7737011289817267</v>
+        <v>0.7807653226368183</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.43017366551382</v>
+        <v>27.5014019573246</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2175,22 +2175,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2460455761416278</v>
+        <v>0.2456593966207025</v>
       </c>
       <c r="C10">
-        <v>567.8668934078942</v>
+        <v>564.4448436701286</v>
       </c>
       <c r="D10">
-        <v>584.7828934078941</v>
+        <v>585.9128436701286</v>
       </c>
       <c r="E10">
-        <v>-227.484</v>
+        <v>-222.932</v>
       </c>
       <c r="F10">
-        <v>36.416</v>
+        <v>40.968</v>
       </c>
       <c r="G10">
         <v>19.5</v>
@@ -2211,28 +2211,28 @@
         <v>50.375</v>
       </c>
       <c r="M10">
-        <v>1.8317248</v>
+        <v>2.0606904</v>
       </c>
       <c r="N10">
-        <v>48.5432752</v>
+        <v>48.3143096</v>
       </c>
       <c r="O10">
-        <v>8.252356784000002</v>
+        <v>8.213432632</v>
       </c>
       <c r="P10">
-        <v>40.290918416</v>
+        <v>40.100876968</v>
       </c>
       <c r="Q10">
-        <v>41.290918416</v>
+        <v>41.100876968</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2638104958061172</v>
+        <v>0.2658263589238489</v>
       </c>
       <c r="T10">
-        <v>0.7807653226368183</v>
+        <v>0.7879847732953186</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.5014019573246</v>
+        <v>24.44569062873297</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2456593966207025</v>
+        <v>0.2452732170997771</v>
       </c>
       <c r="C11">
-        <v>564.4448436701286</v>
+        <v>561.0271690926709</v>
       </c>
       <c r="D11">
-        <v>585.9128436701286</v>
+        <v>587.0471690926709</v>
       </c>
       <c r="E11">
-        <v>-222.932</v>
+        <v>-218.38</v>
       </c>
       <c r="F11">
-        <v>40.968</v>
+        <v>45.52</v>
       </c>
       <c r="G11">
         <v>19.5</v>
@@ -2293,28 +2293,28 @@
         <v>50.375</v>
       </c>
       <c r="M11">
-        <v>2.0606904</v>
+        <v>2.289655999999999</v>
       </c>
       <c r="N11">
-        <v>48.3143096</v>
+        <v>48.085344</v>
       </c>
       <c r="O11">
-        <v>8.213432632</v>
+        <v>8.17450848</v>
       </c>
       <c r="P11">
-        <v>40.100876968</v>
+        <v>39.91083552</v>
       </c>
       <c r="Q11">
-        <v>41.100876968</v>
+        <v>40.91083552</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2658263589238489</v>
+        <v>0.2678870189997524</v>
       </c>
       <c r="T11">
-        <v>0.7879847732953186</v>
+        <v>0.7953646561906743</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.44569062873297</v>
+        <v>22.00112156585968</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2339,22 +2339,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2452732170997771</v>
+        <v>0.2448870375788518</v>
       </c>
       <c r="C12">
-        <v>561.0271690926709</v>
+        <v>557.6138951357011</v>
       </c>
       <c r="D12">
-        <v>587.0471690926709</v>
+        <v>588.1858951357011</v>
       </c>
       <c r="E12">
-        <v>-218.38</v>
+        <v>-213.828</v>
       </c>
       <c r="F12">
-        <v>45.52</v>
+        <v>50.072</v>
       </c>
       <c r="G12">
         <v>19.5</v>
@@ -2375,28 +2375,28 @@
         <v>50.375</v>
       </c>
       <c r="M12">
-        <v>2.289656</v>
+        <v>2.518621599999999</v>
       </c>
       <c r="N12">
-        <v>48.085344</v>
+        <v>47.8563784</v>
       </c>
       <c r="O12">
-        <v>8.17450848</v>
+        <v>8.135584328</v>
       </c>
       <c r="P12">
-        <v>39.91083552</v>
+        <v>39.720794072</v>
       </c>
       <c r="Q12">
-        <v>40.91083552</v>
+        <v>40.720794072</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2678870189997524</v>
+        <v>0.2699939860436537</v>
       </c>
       <c r="T12">
-        <v>0.7953646561906743</v>
+        <v>0.8029103791510942</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.00112156585968</v>
+        <v>20.00101960532698</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2421,22 +2421,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2448870375788518</v>
+        <v>0.2445008580579264</v>
       </c>
       <c r="C13">
-        <v>557.6138951357011</v>
+        <v>554.2050474573299</v>
       </c>
       <c r="D13">
-        <v>588.1858951357011</v>
+        <v>589.3290474573299</v>
       </c>
       <c r="E13">
-        <v>-213.828</v>
+        <v>-209.276</v>
       </c>
       <c r="F13">
-        <v>50.072</v>
+        <v>54.624</v>
       </c>
       <c r="G13">
         <v>19.5</v>
@@ -2457,28 +2457,28 @@
         <v>50.375</v>
       </c>
       <c r="M13">
-        <v>2.518621599999999</v>
+        <v>2.747587199999999</v>
       </c>
       <c r="N13">
-        <v>47.8563784</v>
+        <v>47.6274128</v>
       </c>
       <c r="O13">
-        <v>8.135584328</v>
+        <v>8.096660176</v>
       </c>
       <c r="P13">
-        <v>39.720794072</v>
+        <v>39.530752624</v>
       </c>
       <c r="Q13">
-        <v>40.720794072</v>
+        <v>40.530752624</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2699939860436537</v>
+        <v>0.2721488387021891</v>
       </c>
       <c r="T13">
-        <v>0.8029103791510942</v>
+        <v>0.8106275958151602</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.00101960532698</v>
+        <v>18.33426797154973</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2503,22 +2503,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2445008580579264</v>
+        <v>0.2441146785370011</v>
       </c>
       <c r="C14">
-        <v>554.2050474573299</v>
+        <v>550.8006519155243</v>
       </c>
       <c r="D14">
-        <v>589.3290474573299</v>
+        <v>590.4766519155244</v>
       </c>
       <c r="E14">
-        <v>-209.276</v>
+        <v>-204.724</v>
       </c>
       <c r="F14">
-        <v>54.624</v>
+        <v>59.176</v>
       </c>
       <c r="G14">
         <v>19.5</v>
@@ -2539,28 +2539,28 @@
         <v>50.375</v>
       </c>
       <c r="M14">
-        <v>2.747587199999999</v>
+        <v>2.9765528</v>
       </c>
       <c r="N14">
-        <v>47.6274128</v>
+        <v>47.3984472</v>
       </c>
       <c r="O14">
-        <v>8.096660176</v>
+        <v>8.057736024</v>
       </c>
       <c r="P14">
-        <v>39.530752624</v>
+        <v>39.340711176</v>
       </c>
       <c r="Q14">
-        <v>40.530752624</v>
+        <v>40.340711176</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2721488387021891</v>
+        <v>0.2743532282034495</v>
       </c>
       <c r="T14">
-        <v>0.8106275958151602</v>
+        <v>0.8185222197588596</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.33426797154973</v>
+        <v>16.9239396660459</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2585,22 +2585,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2441146785370011</v>
+        <v>0.2437284990160757</v>
       </c>
       <c r="C15">
-        <v>550.8006519155243</v>
+        <v>547.4007345700583</v>
       </c>
       <c r="D15">
-        <v>590.4766519155244</v>
+        <v>591.6287345700582</v>
       </c>
       <c r="E15">
-        <v>-204.724</v>
+        <v>-200.172</v>
       </c>
       <c r="F15">
-        <v>59.176</v>
+        <v>63.728</v>
       </c>
       <c r="G15">
         <v>19.5</v>
@@ -2621,28 +2621,28 @@
         <v>50.375</v>
       </c>
       <c r="M15">
-        <v>2.9765528</v>
+        <v>3.2055184</v>
       </c>
       <c r="N15">
-        <v>47.3984472</v>
+        <v>47.1694816</v>
       </c>
       <c r="O15">
-        <v>8.057736024</v>
+        <v>8.018811872000001</v>
       </c>
       <c r="P15">
-        <v>39.340711176</v>
+        <v>39.150669728</v>
       </c>
       <c r="Q15">
-        <v>40.340711176</v>
+        <v>40.150669728</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2743532282034495</v>
+        <v>0.2766088825768322</v>
       </c>
       <c r="T15">
-        <v>0.8185222197588596</v>
+        <v>0.8266004396082267</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.9239396660459</v>
+        <v>15.71508683275691</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2667,22 +2667,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2437284990160757</v>
+        <v>0.2433423194951504</v>
       </c>
       <c r="C16">
-        <v>547.4007345700583</v>
+        <v>544.0053216844844</v>
       </c>
       <c r="D16">
-        <v>591.6287345700582</v>
+        <v>592.7853216844844</v>
       </c>
       <c r="E16">
-        <v>-200.172</v>
+        <v>-195.6199999999999</v>
       </c>
       <c r="F16">
-        <v>63.728</v>
+        <v>68.28000000000002</v>
       </c>
       <c r="G16">
         <v>19.5</v>
@@ -2703,28 +2703,28 @@
         <v>50.375</v>
       </c>
       <c r="M16">
-        <v>3.2055184</v>
+        <v>3.434484000000001</v>
       </c>
       <c r="N16">
-        <v>47.1694816</v>
+        <v>46.940516</v>
       </c>
       <c r="O16">
-        <v>8.018811872000001</v>
+        <v>7.979887720000001</v>
       </c>
       <c r="P16">
-        <v>39.150669728</v>
+        <v>38.96062828</v>
       </c>
       <c r="Q16">
-        <v>40.150669728</v>
+        <v>39.96062828</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2766088825768322</v>
+        <v>0.2789176111707651</v>
       </c>
       <c r="T16">
-        <v>0.8266004396082267</v>
+        <v>0.8348687352187552</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.71508683275691</v>
+        <v>14.66741437723978</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2749,22 +2749,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2433423194951504</v>
+        <v>0.242956139974225</v>
       </c>
       <c r="C17">
-        <v>544.0053216844844</v>
+        <v>540.6144397281306</v>
       </c>
       <c r="D17">
-        <v>592.7853216844844</v>
+        <v>593.9464397281306</v>
       </c>
       <c r="E17">
-        <v>-195.62</v>
+        <v>-191.068</v>
       </c>
       <c r="F17">
-        <v>68.28</v>
+        <v>72.83199999999999</v>
       </c>
       <c r="G17">
         <v>19.5</v>
@@ -2785,28 +2785,28 @@
         <v>50.375</v>
       </c>
       <c r="M17">
-        <v>3.434484</v>
+        <v>3.663449599999999</v>
       </c>
       <c r="N17">
-        <v>46.940516</v>
+        <v>46.7115504</v>
       </c>
       <c r="O17">
-        <v>7.979887720000001</v>
+        <v>7.940963568000001</v>
       </c>
       <c r="P17">
-        <v>38.96062828</v>
+        <v>38.770586832</v>
       </c>
       <c r="Q17">
-        <v>39.96062828</v>
+        <v>39.770586832</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2789176111707651</v>
+        <v>0.281281309493125</v>
       </c>
       <c r="T17">
-        <v>0.8348687352187552</v>
+        <v>0.8433338950104868</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.66741437723979</v>
+        <v>13.7507009786623</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2831,22 +2831,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.242956139974225</v>
+        <v>0.2425699604532997</v>
       </c>
       <c r="C18">
-        <v>540.6144397281306</v>
+        <v>537.2281153781186</v>
       </c>
       <c r="D18">
-        <v>593.9464397281306</v>
+        <v>595.1121153781186</v>
       </c>
       <c r="E18">
-        <v>-191.068</v>
+        <v>-186.516</v>
       </c>
       <c r="F18">
-        <v>72.83199999999999</v>
+        <v>77.384</v>
       </c>
       <c r="G18">
         <v>19.5</v>
@@ -2867,28 +2867,28 @@
         <v>50.375</v>
       </c>
       <c r="M18">
-        <v>3.663449599999999</v>
+        <v>3.8924152</v>
       </c>
       <c r="N18">
-        <v>46.7115504</v>
+        <v>46.4825848</v>
       </c>
       <c r="O18">
-        <v>7.940963568000001</v>
+        <v>7.902039416</v>
       </c>
       <c r="P18">
-        <v>38.770586832</v>
+        <v>38.580545384</v>
       </c>
       <c r="Q18">
-        <v>39.770586832</v>
+        <v>39.580545384</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.281281309493125</v>
+        <v>0.2837019644015659</v>
       </c>
       <c r="T18">
-        <v>0.8433338950104868</v>
+        <v>0.852003034556236</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.7507009786623</v>
+        <v>12.94183621521157</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2425699604532997</v>
+        <v>0.2424078809323743</v>
       </c>
       <c r="C19">
-        <v>537.2281153781186</v>
+        <v>533.1667136496625</v>
       </c>
       <c r="D19">
-        <v>595.1121153781186</v>
+        <v>595.6027136496625</v>
       </c>
       <c r="E19">
-        <v>-186.516</v>
+        <v>-181.964</v>
       </c>
       <c r="F19">
-        <v>77.384</v>
+        <v>81.93600000000001</v>
       </c>
       <c r="G19">
         <v>19.5</v>
@@ -2949,45 +2949,45 @@
         <v>50.375</v>
       </c>
       <c r="M19">
-        <v>3.8924152</v>
+        <v>4.2442848</v>
       </c>
       <c r="N19">
-        <v>46.4825848</v>
+        <v>46.1307152</v>
       </c>
       <c r="O19">
-        <v>7.902039416</v>
+        <v>7.842221584</v>
       </c>
       <c r="P19">
-        <v>38.580545384</v>
+        <v>38.288493616</v>
       </c>
       <c r="Q19">
-        <v>39.580545384</v>
+        <v>39.288493616</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2837019644015659</v>
+        <v>0.2861816596736272</v>
       </c>
       <c r="T19">
-        <v>0.852003034556236</v>
+        <v>0.8608836165299304</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.17</v>
       </c>
       <c r="W19">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.94183621521157</v>
+        <v>11.86890191723232</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2995,22 +2995,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2424078809323744</v>
+        <v>0.242034151411449</v>
       </c>
       <c r="C20">
-        <v>533.1667136496624</v>
+        <v>529.7490438120378</v>
       </c>
       <c r="D20">
-        <v>595.6027136496624</v>
+        <v>596.7370438120379</v>
       </c>
       <c r="E20">
-        <v>-181.964</v>
+        <v>-177.412</v>
       </c>
       <c r="F20">
-        <v>81.93599999999999</v>
+        <v>86.488</v>
       </c>
       <c r="G20">
         <v>19.5</v>
@@ -3031,28 +3031,28 @@
         <v>50.375</v>
       </c>
       <c r="M20">
-        <v>4.2442848</v>
+        <v>4.4800784</v>
       </c>
       <c r="N20">
-        <v>46.1307152</v>
+        <v>45.8949216</v>
       </c>
       <c r="O20">
-        <v>7.842221584</v>
+        <v>7.802136672000001</v>
       </c>
       <c r="P20">
-        <v>38.288493616</v>
+        <v>38.092784928</v>
       </c>
       <c r="Q20">
-        <v>39.288493616</v>
+        <v>39.092784928</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2861816596736272</v>
+        <v>0.2887225819894432</v>
       </c>
       <c r="T20">
-        <v>0.8608836165299304</v>
+        <v>0.8699834721326049</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.86890191723232</v>
+        <v>11.24422286895694</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3077,22 +3077,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.242034151411449</v>
+        <v>0.2416604218905236</v>
       </c>
       <c r="C21">
-        <v>529.7490438120378</v>
+        <v>526.3357029007381</v>
       </c>
       <c r="D21">
-        <v>596.7370438120379</v>
+        <v>597.875702900738</v>
       </c>
       <c r="E21">
-        <v>-177.412</v>
+        <v>-172.86</v>
       </c>
       <c r="F21">
-        <v>86.488</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="G21">
         <v>19.5</v>
@@ -3113,28 +3113,28 @@
         <v>50.375</v>
       </c>
       <c r="M21">
-        <v>4.4800784</v>
+        <v>4.715872</v>
       </c>
       <c r="N21">
-        <v>45.8949216</v>
+        <v>45.659128</v>
       </c>
       <c r="O21">
-        <v>7.802136672000001</v>
+        <v>7.762051760000001</v>
       </c>
       <c r="P21">
-        <v>38.092784928</v>
+        <v>37.89707624</v>
       </c>
       <c r="Q21">
-        <v>39.092784928</v>
+        <v>38.89707624</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2887225819894432</v>
+        <v>0.2913270273631545</v>
       </c>
       <c r="T21">
-        <v>0.8699834721326049</v>
+        <v>0.8793108241253462</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.24422286895694</v>
+        <v>10.68201172550909</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3159,22 +3159,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2416604218905236</v>
+        <v>0.2412866923695983</v>
       </c>
       <c r="C22">
-        <v>526.3357029007381</v>
+        <v>522.9267157437582</v>
       </c>
       <c r="D22">
-        <v>597.875702900738</v>
+        <v>599.0187157437582</v>
       </c>
       <c r="E22">
-        <v>-172.86</v>
+        <v>-168.308</v>
       </c>
       <c r="F22">
-        <v>91.04000000000001</v>
+        <v>95.59200000000001</v>
       </c>
       <c r="G22">
         <v>19.5</v>
@@ -3195,28 +3195,28 @@
         <v>50.375</v>
       </c>
       <c r="M22">
-        <v>4.715872</v>
+        <v>4.951665600000001</v>
       </c>
       <c r="N22">
-        <v>45.659128</v>
+        <v>45.4233344</v>
       </c>
       <c r="O22">
-        <v>7.762051760000001</v>
+        <v>7.721966848000001</v>
       </c>
       <c r="P22">
-        <v>37.89707624</v>
+        <v>37.701367552</v>
       </c>
       <c r="Q22">
-        <v>38.89707624</v>
+        <v>38.701367552</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2913270273631545</v>
+        <v>0.2939974080627826</v>
       </c>
       <c r="T22">
-        <v>0.8793108241253462</v>
+        <v>0.8888743116115746</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.68201172550909</v>
+        <v>10.17334450048484</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3241,22 +3241,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2412866923695983</v>
+        <v>0.2412233828486729</v>
       </c>
       <c r="C23">
-        <v>522.9267157437582</v>
+        <v>518.5687743429199</v>
       </c>
       <c r="D23">
-        <v>599.0187157437582</v>
+        <v>599.2127743429199</v>
       </c>
       <c r="E23">
-        <v>-168.308</v>
+        <v>-163.756</v>
       </c>
       <c r="F23">
-        <v>95.592</v>
+        <v>100.144</v>
       </c>
       <c r="G23">
         <v>19.5</v>
@@ -3277,45 +3277,45 @@
         <v>50.375</v>
       </c>
       <c r="M23">
-        <v>4.9516656</v>
+        <v>5.357703999999999</v>
       </c>
       <c r="N23">
-        <v>45.4233344</v>
+        <v>45.017296</v>
       </c>
       <c r="O23">
-        <v>7.721966848000001</v>
+        <v>7.652940320000001</v>
       </c>
       <c r="P23">
-        <v>37.701367552</v>
+        <v>37.36435568</v>
       </c>
       <c r="Q23">
-        <v>38.701367552</v>
+        <v>38.36435568</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2939974080627826</v>
+        <v>0.2967362600624012</v>
       </c>
       <c r="T23">
-        <v>0.8888743116115746</v>
+        <v>0.898683016725655</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.17</v>
       </c>
       <c r="W23">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.17334450048485</v>
+        <v>9.402348468672404</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3323,22 +3323,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2412233828486729</v>
+        <v>0.2408637633277476</v>
       </c>
       <c r="C24">
-        <v>518.5687743429199</v>
+        <v>515.121482911879</v>
       </c>
       <c r="D24">
-        <v>599.2127743429199</v>
+        <v>600.317482911879</v>
       </c>
       <c r="E24">
-        <v>-163.756</v>
+        <v>-159.204</v>
       </c>
       <c r="F24">
-        <v>100.144</v>
+        <v>104.696</v>
       </c>
       <c r="G24">
         <v>19.5</v>
@@ -3359,28 +3359,28 @@
         <v>50.375</v>
       </c>
       <c r="M24">
-        <v>5.357703999999999</v>
+        <v>5.601236</v>
       </c>
       <c r="N24">
-        <v>45.017296</v>
+        <v>44.773764</v>
       </c>
       <c r="O24">
-        <v>7.652940320000001</v>
+        <v>7.61153988</v>
       </c>
       <c r="P24">
-        <v>37.36435568</v>
+        <v>37.16222412</v>
       </c>
       <c r="Q24">
-        <v>38.36435568</v>
+        <v>38.16222412</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2967362600624012</v>
+        <v>0.2995462510749968</v>
       </c>
       <c r="T24">
-        <v>0.898683016725655</v>
+        <v>0.9087464934011402</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.402348468672404</v>
+        <v>8.993550709164905</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3405,22 +3405,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2408637633277476</v>
+        <v>0.2405041438068222</v>
       </c>
       <c r="C25">
-        <v>515.121482911879</v>
+        <v>511.6782722852683</v>
       </c>
       <c r="D25">
-        <v>600.317482911879</v>
+        <v>601.4262722852683</v>
       </c>
       <c r="E25">
-        <v>-159.204</v>
+        <v>-154.652</v>
       </c>
       <c r="F25">
-        <v>104.696</v>
+        <v>109.248</v>
       </c>
       <c r="G25">
         <v>19.5</v>
@@ -3441,28 +3441,28 @@
         <v>50.375</v>
       </c>
       <c r="M25">
-        <v>5.601236</v>
+        <v>5.844768</v>
       </c>
       <c r="N25">
-        <v>44.773764</v>
+        <v>44.530232</v>
       </c>
       <c r="O25">
-        <v>7.61153988</v>
+        <v>7.57013944</v>
       </c>
       <c r="P25">
-        <v>37.16222412</v>
+        <v>36.96009256</v>
       </c>
       <c r="Q25">
-        <v>38.16222412</v>
+        <v>37.96009256</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2995462510749968</v>
+        <v>0.3024301892195029</v>
       </c>
       <c r="T25">
-        <v>0.9087464934011402</v>
+        <v>0.9190747984101907</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.993550709164905</v>
+        <v>8.618819429616368</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3487,22 +3487,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2405041438068222</v>
+        <v>0.2401445242858969</v>
       </c>
       <c r="C26">
-        <v>511.6782722852683</v>
+        <v>508.2391651167275</v>
       </c>
       <c r="D26">
-        <v>601.4262722852683</v>
+        <v>602.5391651167275</v>
       </c>
       <c r="E26">
-        <v>-154.652</v>
+        <v>-150.1</v>
       </c>
       <c r="F26">
-        <v>109.248</v>
+        <v>113.8</v>
       </c>
       <c r="G26">
         <v>19.5</v>
@@ -3523,28 +3523,28 @@
         <v>50.375</v>
       </c>
       <c r="M26">
-        <v>5.844767999999999</v>
+        <v>6.088299999999999</v>
       </c>
       <c r="N26">
-        <v>44.530232</v>
+        <v>44.2867</v>
       </c>
       <c r="O26">
-        <v>7.57013944</v>
+        <v>7.528739000000001</v>
       </c>
       <c r="P26">
-        <v>36.96009256</v>
+        <v>36.757961</v>
       </c>
       <c r="Q26">
-        <v>37.96009256</v>
+        <v>37.757961</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.3024301892195029</v>
+        <v>0.3053910323811959</v>
       </c>
       <c r="T26">
-        <v>0.9190747984101907</v>
+        <v>0.9296785248861493</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.618819429616369</v>
+        <v>8.274066652431713</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3569,22 +3569,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2401445242858969</v>
+        <v>0.2397849047649716</v>
       </c>
       <c r="C27">
-        <v>508.2391651167275</v>
+        <v>504.8041842278825</v>
       </c>
       <c r="D27">
-        <v>602.5391651167275</v>
+        <v>603.6561842278825</v>
       </c>
       <c r="E27">
-        <v>-150.1</v>
+        <v>-145.548</v>
       </c>
       <c r="F27">
-        <v>113.8</v>
+        <v>118.352</v>
       </c>
       <c r="G27">
         <v>19.5</v>
@@ -3605,28 +3605,28 @@
         <v>50.375</v>
       </c>
       <c r="M27">
-        <v>6.088299999999999</v>
+        <v>6.331832</v>
       </c>
       <c r="N27">
-        <v>44.2867</v>
+        <v>44.043168</v>
       </c>
       <c r="O27">
-        <v>7.528739000000001</v>
+        <v>7.48733856</v>
       </c>
       <c r="P27">
-        <v>36.757961</v>
+        <v>36.55582944</v>
       </c>
       <c r="Q27">
-        <v>37.757961</v>
+        <v>37.55582944</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.3053910323811959</v>
+        <v>0.3084318983310426</v>
       </c>
       <c r="T27">
-        <v>0.9296785248861493</v>
+        <v>0.9405688385641608</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.274066652431713</v>
+        <v>7.955833319645878</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3651,22 +3651,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2397849047649716</v>
+        <v>0.2394252852440462</v>
       </c>
       <c r="C28">
-        <v>504.8041842278825</v>
+        <v>501.3733526099048</v>
       </c>
       <c r="D28">
-        <v>603.6561842278825</v>
+        <v>604.7773526099048</v>
       </c>
       <c r="E28">
-        <v>-145.548</v>
+        <v>-140.996</v>
       </c>
       <c r="F28">
-        <v>118.352</v>
+        <v>122.904</v>
       </c>
       <c r="G28">
         <v>19.5</v>
@@ -3687,28 +3687,28 @@
         <v>50.375</v>
       </c>
       <c r="M28">
-        <v>6.331832</v>
+        <v>6.575364</v>
       </c>
       <c r="N28">
-        <v>44.043168</v>
+        <v>43.799636</v>
       </c>
       <c r="O28">
-        <v>7.48733856</v>
+        <v>7.44593812</v>
       </c>
       <c r="P28">
-        <v>36.55582944</v>
+        <v>36.35369788</v>
       </c>
       <c r="Q28">
-        <v>37.55582944</v>
+        <v>37.35369788</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.3084318983310426</v>
+        <v>0.3115560756767756</v>
       </c>
       <c r="T28">
-        <v>0.9405688385641608</v>
+        <v>0.951757517000474</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.955833319645878</v>
+        <v>7.66117282632566</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3733,22 +3733,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2394252852440462</v>
+        <v>0.2392515857231208</v>
       </c>
       <c r="C29">
-        <v>501.3733526099048</v>
+        <v>497.3643801380698</v>
       </c>
       <c r="D29">
-        <v>604.7773526099048</v>
+        <v>605.3203801380698</v>
       </c>
       <c r="E29">
-        <v>-140.996</v>
+        <v>-136.444</v>
       </c>
       <c r="F29">
-        <v>122.904</v>
+        <v>127.456</v>
       </c>
       <c r="G29">
         <v>19.5</v>
@@ -3769,45 +3769,45 @@
         <v>50.375</v>
       </c>
       <c r="M29">
-        <v>6.575364</v>
+        <v>6.920860800000001</v>
       </c>
       <c r="N29">
-        <v>43.799636</v>
+        <v>43.4541392</v>
       </c>
       <c r="O29">
-        <v>7.44593812</v>
+        <v>7.387203664</v>
       </c>
       <c r="P29">
-        <v>36.35369788</v>
+        <v>36.066935536</v>
       </c>
       <c r="Q29">
-        <v>37.35369788</v>
+        <v>37.066935536</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.3115560756767756</v>
+        <v>0.3147670357265567</v>
       </c>
       <c r="T29">
-        <v>0.951757517000474</v>
+        <v>0.9632569920600181</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.17</v>
       </c>
       <c r="W29">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.66117282632566</v>
+        <v>7.278718855319268</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3815,22 +3815,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2392515857231208</v>
+        <v>0.2388986062021955</v>
       </c>
       <c r="C30">
-        <v>497.3643801380698</v>
+        <v>493.9188909616837</v>
       </c>
       <c r="D30">
-        <v>605.3203801380698</v>
+        <v>606.4268909616837</v>
       </c>
       <c r="E30">
-        <v>-136.444</v>
+        <v>-131.892</v>
       </c>
       <c r="F30">
-        <v>127.456</v>
+        <v>132.008</v>
       </c>
       <c r="G30">
         <v>19.5</v>
@@ -3851,28 +3851,28 @@
         <v>50.375</v>
       </c>
       <c r="M30">
-        <v>6.920860800000001</v>
+        <v>7.168034400000001</v>
       </c>
       <c r="N30">
-        <v>43.4541392</v>
+        <v>43.2069656</v>
       </c>
       <c r="O30">
-        <v>7.387203664</v>
+        <v>7.345184152</v>
       </c>
       <c r="P30">
-        <v>36.066935536</v>
+        <v>35.861781448</v>
       </c>
       <c r="Q30">
-        <v>37.066935536</v>
+        <v>36.861781448</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.3147670357265567</v>
+        <v>0.3180684453552049</v>
       </c>
       <c r="T30">
-        <v>0.9632569920600181</v>
+        <v>0.975080395994479</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.278718855319268</v>
+        <v>7.027728549963431</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3897,22 +3897,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2388986062021954</v>
+        <v>0.2385456266812701</v>
       </c>
       <c r="C31">
-        <v>493.918890961684</v>
+        <v>490.4774545429883</v>
       </c>
       <c r="D31">
-        <v>606.426890961684</v>
+        <v>607.5374545429883</v>
       </c>
       <c r="E31">
-        <v>-131.892</v>
+        <v>-127.34</v>
       </c>
       <c r="F31">
-        <v>132.008</v>
+        <v>136.56</v>
       </c>
       <c r="G31">
         <v>19.5</v>
@@ -3933,28 +3933,28 @@
         <v>50.375</v>
       </c>
       <c r="M31">
-        <v>7.168034399999999</v>
+        <v>7.415208000000001</v>
       </c>
       <c r="N31">
-        <v>43.2069656</v>
+        <v>42.959792</v>
       </c>
       <c r="O31">
-        <v>7.345184152000001</v>
+        <v>7.30316464</v>
       </c>
       <c r="P31">
-        <v>35.861781448</v>
+        <v>35.65662736</v>
       </c>
       <c r="Q31">
-        <v>36.861781448</v>
+        <v>36.65662736</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.3180684453552048</v>
+        <v>0.321464180973243</v>
       </c>
       <c r="T31">
-        <v>0.9750803959944788</v>
+        <v>0.9872416114699243</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.027728549963434</v>
+        <v>6.793470931631317</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2385456266812701</v>
+        <v>0.2381926471603447</v>
       </c>
       <c r="C32">
-        <v>490.4774545429883</v>
+        <v>487.04009318856</v>
       </c>
       <c r="D32">
-        <v>607.5374545429883</v>
+        <v>608.65209318856</v>
       </c>
       <c r="E32">
-        <v>-127.34</v>
+        <v>-122.788</v>
       </c>
       <c r="F32">
-        <v>136.56</v>
+        <v>141.112</v>
       </c>
       <c r="G32">
         <v>19.5</v>
@@ -4015,28 +4015,28 @@
         <v>50.375</v>
       </c>
       <c r="M32">
-        <v>7.415208000000001</v>
+        <v>7.6623816</v>
       </c>
       <c r="N32">
-        <v>42.959792</v>
+        <v>42.7126184</v>
       </c>
       <c r="O32">
-        <v>7.30316464</v>
+        <v>7.261145128</v>
       </c>
       <c r="P32">
-        <v>35.65662736</v>
+        <v>35.45147327199999</v>
       </c>
       <c r="Q32">
-        <v>36.65662736</v>
+        <v>36.45147327199999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.321464180973243</v>
+        <v>0.3249583437106446</v>
       </c>
       <c r="T32">
-        <v>0.9872416114699243</v>
+        <v>0.999755325944658</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.793470931631317</v>
+        <v>6.574326708030307</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4061,22 +4061,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2381926471603447</v>
+        <v>0.2378396676394194</v>
       </c>
       <c r="C33">
-        <v>487.04009318856</v>
+        <v>483.6068293689793</v>
       </c>
       <c r="D33">
-        <v>608.65209318856</v>
+        <v>609.7708293689793</v>
       </c>
       <c r="E33">
-        <v>-122.788</v>
+        <v>-118.236</v>
       </c>
       <c r="F33">
-        <v>141.112</v>
+        <v>145.664</v>
       </c>
       <c r="G33">
         <v>19.5</v>
@@ -4097,28 +4097,28 @@
         <v>50.375</v>
       </c>
       <c r="M33">
-        <v>7.6623816</v>
+        <v>7.9095552</v>
       </c>
       <c r="N33">
-        <v>42.7126184</v>
+        <v>42.4654448</v>
       </c>
       <c r="O33">
-        <v>7.261145128</v>
+        <v>7.219125616</v>
       </c>
       <c r="P33">
-        <v>35.45147327199999</v>
+        <v>35.246319184</v>
       </c>
       <c r="Q33">
-        <v>36.45147327199999</v>
+        <v>36.246319184</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.3249583437106446</v>
+        <v>0.3285552759403227</v>
       </c>
       <c r="T33">
-        <v>0.999755325944658</v>
+        <v>1.012637090845119</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.574326708030307</v>
+        <v>6.368878998404361</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4143,22 +4143,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2378396676394194</v>
+        <v>0.237486688118494</v>
       </c>
       <c r="C34">
-        <v>483.6068293689793</v>
+        <v>480.1776857203388</v>
       </c>
       <c r="D34">
-        <v>609.7708293689793</v>
+        <v>610.8936857203388</v>
       </c>
       <c r="E34">
-        <v>-118.236</v>
+        <v>-113.684</v>
       </c>
       <c r="F34">
-        <v>145.664</v>
+        <v>150.216</v>
       </c>
       <c r="G34">
         <v>19.5</v>
@@ -4179,28 +4179,28 @@
         <v>50.375</v>
       </c>
       <c r="M34">
-        <v>7.9095552</v>
+        <v>8.1567288</v>
       </c>
       <c r="N34">
-        <v>42.4654448</v>
+        <v>42.2182712</v>
       </c>
       <c r="O34">
-        <v>7.219125616</v>
+        <v>7.177106104000001</v>
       </c>
       <c r="P34">
-        <v>35.246319184</v>
+        <v>35.041165096</v>
       </c>
       <c r="Q34">
-        <v>36.246319184</v>
+        <v>36.041165096</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.3285552759403227</v>
+        <v>0.3322595792813344</v>
       </c>
       <c r="T34">
-        <v>1.012637090845119</v>
+        <v>1.025903386041117</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.368878998404361</v>
+        <v>6.175882665119381</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4225,22 +4225,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.237486688118494</v>
+        <v>0.2374159085975687</v>
       </c>
       <c r="C35">
-        <v>480.1776857203388</v>
+        <v>475.8513390219257</v>
       </c>
       <c r="D35">
-        <v>610.8936857203388</v>
+        <v>611.1193390219257</v>
       </c>
       <c r="E35">
-        <v>-113.684</v>
+        <v>-109.132</v>
       </c>
       <c r="F35">
-        <v>150.216</v>
+        <v>154.768</v>
       </c>
       <c r="G35">
         <v>19.5</v>
@@ -4261,45 +4261,45 @@
         <v>50.375</v>
       </c>
       <c r="M35">
-        <v>8.1567288</v>
+        <v>8.5586704</v>
       </c>
       <c r="N35">
-        <v>42.2182712</v>
+        <v>41.8163296</v>
       </c>
       <c r="O35">
-        <v>7.177106104000001</v>
+        <v>7.108776032000001</v>
       </c>
       <c r="P35">
-        <v>35.041165096</v>
+        <v>34.707553568</v>
       </c>
       <c r="Q35">
-        <v>36.041165096</v>
+        <v>35.707553568</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3322595792813344</v>
+        <v>0.3360761342387405</v>
       </c>
       <c r="T35">
-        <v>1.025903386041117</v>
+        <v>1.039571690182447</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.17</v>
       </c>
       <c r="W35">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.175882665119381</v>
+        <v>5.885844137659513</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4307,22 +4307,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2374159085975687</v>
+        <v>0.2370712290766434</v>
       </c>
       <c r="C36">
-        <v>475.8513390219257</v>
+        <v>472.4006040789818</v>
       </c>
       <c r="D36">
-        <v>611.1193390219257</v>
+        <v>612.2206040789819</v>
       </c>
       <c r="E36">
-        <v>-109.132</v>
+        <v>-104.58</v>
       </c>
       <c r="F36">
-        <v>154.768</v>
+        <v>159.32</v>
       </c>
       <c r="G36">
         <v>19.5</v>
@@ -4343,28 +4343,28 @@
         <v>50.375</v>
       </c>
       <c r="M36">
-        <v>8.5586704</v>
+        <v>8.810396000000001</v>
       </c>
       <c r="N36">
-        <v>41.8163296</v>
+        <v>41.564604</v>
       </c>
       <c r="O36">
-        <v>7.108776032000001</v>
+        <v>7.065982680000001</v>
       </c>
       <c r="P36">
-        <v>34.707553568</v>
+        <v>34.49862132</v>
       </c>
       <c r="Q36">
-        <v>35.707553568</v>
+        <v>35.49862132</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3360761342387405</v>
+        <v>0.3400101216563744</v>
       </c>
       <c r="T36">
-        <v>1.039571690182447</v>
+        <v>1.053660557528126</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.885844137659513</v>
+        <v>5.717677162297813</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4389,22 +4389,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2370712290766434</v>
+        <v>0.236726549555718</v>
       </c>
       <c r="C37">
-        <v>472.4006040789818</v>
+        <v>468.9538453615883</v>
       </c>
       <c r="D37">
-        <v>612.2206040789819</v>
+        <v>613.3258453615883</v>
       </c>
       <c r="E37">
-        <v>-104.58</v>
+        <v>-100.028</v>
       </c>
       <c r="F37">
-        <v>159.32</v>
+        <v>163.872</v>
       </c>
       <c r="G37">
         <v>19.5</v>
@@ -4425,28 +4425,28 @@
         <v>50.375</v>
       </c>
       <c r="M37">
-        <v>8.810396000000001</v>
+        <v>9.062121600000001</v>
       </c>
       <c r="N37">
-        <v>41.564604</v>
+        <v>41.3128784</v>
       </c>
       <c r="O37">
-        <v>7.065982680000001</v>
+        <v>7.023189328000001</v>
       </c>
       <c r="P37">
-        <v>34.49862132</v>
+        <v>34.289689072</v>
       </c>
       <c r="Q37">
-        <v>35.49862132</v>
+        <v>35.289689072</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3400101216563744</v>
+        <v>0.3440670461808094</v>
       </c>
       <c r="T37">
-        <v>1.053660557528126</v>
+        <v>1.068189701978358</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.717677162297813</v>
+        <v>5.558852796678429</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4471,22 +4471,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.236726549555718</v>
+        <v>0.2363818700347927</v>
       </c>
       <c r="C38">
-        <v>468.9538453615882</v>
+        <v>465.5110844435206</v>
       </c>
       <c r="D38">
-        <v>613.3258453615881</v>
+        <v>614.4350844435206</v>
       </c>
       <c r="E38">
-        <v>-100.028</v>
+        <v>-95.47599999999997</v>
       </c>
       <c r="F38">
-        <v>163.872</v>
+        <v>168.424</v>
       </c>
       <c r="G38">
         <v>19.5</v>
@@ -4507,28 +4507,28 @@
         <v>50.375</v>
       </c>
       <c r="M38">
-        <v>9.062121599999999</v>
+        <v>9.313847200000001</v>
       </c>
       <c r="N38">
-        <v>41.3128784</v>
+        <v>41.0611528</v>
       </c>
       <c r="O38">
-        <v>7.023189328000001</v>
+        <v>6.980395976000001</v>
       </c>
       <c r="P38">
-        <v>34.289689072</v>
+        <v>34.08075682400001</v>
       </c>
       <c r="Q38">
-        <v>35.289689072</v>
+        <v>35.08075682400001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3440670461808094</v>
+        <v>0.3482527619599883</v>
       </c>
       <c r="T38">
-        <v>1.068189701978358</v>
+        <v>1.083180089109549</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.55885279667843</v>
+        <v>5.408613531903335</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4553,22 +4553,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2363818700347927</v>
+        <v>0.2360371905138673</v>
       </c>
       <c r="C39">
-        <v>465.5110844435206</v>
+        <v>462.0723430549082</v>
       </c>
       <c r="D39">
-        <v>614.4350844435206</v>
+        <v>615.5483430549082</v>
       </c>
       <c r="E39">
-        <v>-95.47599999999997</v>
+        <v>-90.92399999999998</v>
       </c>
       <c r="F39">
-        <v>168.424</v>
+        <v>172.976</v>
       </c>
       <c r="G39">
         <v>19.5</v>
@@ -4589,28 +4589,28 @@
         <v>50.375</v>
       </c>
       <c r="M39">
-        <v>9.313847200000001</v>
+        <v>9.5655728</v>
       </c>
       <c r="N39">
-        <v>41.0611528</v>
+        <v>40.8094272</v>
       </c>
       <c r="O39">
-        <v>6.980395976000001</v>
+        <v>6.937602624000001</v>
       </c>
       <c r="P39">
-        <v>34.08075682400001</v>
+        <v>33.871824576</v>
       </c>
       <c r="Q39">
-        <v>35.08075682400001</v>
+        <v>34.871824576</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3482527619599883</v>
+        <v>0.3525735008288182</v>
       </c>
       <c r="T39">
-        <v>1.083180089109549</v>
+        <v>1.098654037115941</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.408613531903335</v>
+        <v>5.266281596853249</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4635,22 +4635,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2360371905138673</v>
+        <v>0.2356925109929419</v>
       </c>
       <c r="C40">
-        <v>462.0723430549082</v>
+        <v>458.6376430836515</v>
       </c>
       <c r="D40">
-        <v>615.5483430549082</v>
+        <v>616.6656430836515</v>
       </c>
       <c r="E40">
-        <v>-90.92399999999998</v>
+        <v>-86.37199999999999</v>
       </c>
       <c r="F40">
-        <v>172.976</v>
+        <v>177.528</v>
       </c>
       <c r="G40">
         <v>19.5</v>
@@ -4671,28 +4671,28 @@
         <v>50.375</v>
       </c>
       <c r="M40">
-        <v>9.5655728</v>
+        <v>9.8172984</v>
       </c>
       <c r="N40">
-        <v>40.8094272</v>
+        <v>40.5577016</v>
       </c>
       <c r="O40">
-        <v>6.937602624000001</v>
+        <v>6.894809272000001</v>
       </c>
       <c r="P40">
-        <v>33.871824576</v>
+        <v>33.662892328</v>
       </c>
       <c r="Q40">
-        <v>34.871824576</v>
+        <v>34.662892328</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3525735008288182</v>
+        <v>0.3570359032671179</v>
       </c>
       <c r="T40">
-        <v>1.098654037115941</v>
+        <v>1.114635327679918</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.266281596853249</v>
+        <v>5.131248735395473</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4717,22 +4717,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2356925109929419</v>
+        <v>0.2353478314720166</v>
       </c>
       <c r="C41">
-        <v>458.6376430836515</v>
+        <v>455.207006576858</v>
       </c>
       <c r="D41">
-        <v>616.6656430836515</v>
+        <v>617.7870065768581</v>
       </c>
       <c r="E41">
-        <v>-86.37199999999999</v>
+        <v>-81.81999999999996</v>
       </c>
       <c r="F41">
-        <v>177.528</v>
+        <v>182.08</v>
       </c>
       <c r="G41">
         <v>19.5</v>
@@ -4753,28 +4753,28 @@
         <v>50.375</v>
       </c>
       <c r="M41">
-        <v>9.8172984</v>
+        <v>10.069024</v>
       </c>
       <c r="N41">
-        <v>40.5577016</v>
+        <v>40.305976</v>
       </c>
       <c r="O41">
-        <v>6.894809272000001</v>
+        <v>6.85201592</v>
       </c>
       <c r="P41">
-        <v>33.662892328</v>
+        <v>33.45396008</v>
       </c>
       <c r="Q41">
-        <v>34.662892328</v>
+        <v>34.45396008</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3570359032671179</v>
+        <v>0.361647052453361</v>
       </c>
       <c r="T41">
-        <v>1.114635327679918</v>
+        <v>1.131149327929362</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.131248735395473</v>
+        <v>5.002967517010586</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4799,22 +4799,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2353478314720166</v>
+        <v>0.2350031519510912</v>
       </c>
       <c r="C42">
-        <v>455.207006576858</v>
+        <v>451.7804557422921</v>
       </c>
       <c r="D42">
-        <v>617.7870065768581</v>
+        <v>618.9124557422921</v>
       </c>
       <c r="E42">
-        <v>-81.81999999999996</v>
+        <v>-77.26799999999997</v>
       </c>
       <c r="F42">
-        <v>182.08</v>
+        <v>186.632</v>
       </c>
       <c r="G42">
         <v>19.5</v>
@@ -4835,28 +4835,28 @@
         <v>50.375</v>
       </c>
       <c r="M42">
-        <v>10.069024</v>
+        <v>10.3207496</v>
       </c>
       <c r="N42">
-        <v>40.305976</v>
+        <v>40.0542504</v>
       </c>
       <c r="O42">
-        <v>6.85201592</v>
+        <v>6.809222568000001</v>
       </c>
       <c r="P42">
-        <v>33.45396008</v>
+        <v>33.245027832</v>
       </c>
       <c r="Q42">
-        <v>34.45396008</v>
+        <v>34.245027832</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.361647052453361</v>
+        <v>0.3664145117815105</v>
       </c>
       <c r="T42">
-        <v>1.131149327929362</v>
+        <v>1.148223124797431</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.002967517010586</v>
+        <v>4.880943919034718</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4881,22 +4881,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2350031519510912</v>
+        <v>0.2346584724301659</v>
       </c>
       <c r="C43">
-        <v>451.7804557422921</v>
+        <v>448.35801294984</v>
       </c>
       <c r="D43">
-        <v>618.9124557422921</v>
+        <v>620.04201294984</v>
       </c>
       <c r="E43">
-        <v>-77.26799999999997</v>
+        <v>-72.71599999999995</v>
       </c>
       <c r="F43">
-        <v>186.632</v>
+        <v>191.184</v>
       </c>
       <c r="G43">
         <v>19.5</v>
@@ -4917,28 +4917,28 @@
         <v>50.375</v>
       </c>
       <c r="M43">
-        <v>10.3207496</v>
+        <v>10.5724752</v>
       </c>
       <c r="N43">
-        <v>40.0542504</v>
+        <v>39.8025248</v>
       </c>
       <c r="O43">
-        <v>6.809222568000001</v>
+        <v>6.766429216000001</v>
       </c>
       <c r="P43">
-        <v>33.245027832</v>
+        <v>33.036095584</v>
       </c>
       <c r="Q43">
-        <v>34.245027832</v>
+        <v>34.036095584</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3664145117815105</v>
+        <v>0.3713463662589067</v>
       </c>
       <c r="T43">
-        <v>1.148223124797431</v>
+        <v>1.16588567328164</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.880943919034718</v>
+        <v>4.76473096858151</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4963,22 +4963,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2346584724301659</v>
+        <v>0.2343137929092406</v>
       </c>
       <c r="C44">
-        <v>448.35801294984</v>
+        <v>444.9397007329934</v>
       </c>
       <c r="D44">
-        <v>620.04201294984</v>
+        <v>621.1757007329934</v>
       </c>
       <c r="E44">
-        <v>-72.71599999999998</v>
+        <v>-68.16399999999999</v>
       </c>
       <c r="F44">
-        <v>191.184</v>
+        <v>195.736</v>
       </c>
       <c r="G44">
         <v>19.5</v>
@@ -4999,28 +4999,28 @@
         <v>50.375</v>
       </c>
       <c r="M44">
-        <v>10.5724752</v>
+        <v>10.8242008</v>
       </c>
       <c r="N44">
-        <v>39.8025248</v>
+        <v>39.5507992</v>
       </c>
       <c r="O44">
-        <v>6.766429216000001</v>
+        <v>6.723635864</v>
       </c>
       <c r="P44">
-        <v>33.036095584</v>
+        <v>32.827163336</v>
       </c>
       <c r="Q44">
-        <v>34.036095584</v>
+        <v>33.827163336</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3713463662589067</v>
+        <v>0.3764512682618255</v>
       </c>
       <c r="T44">
-        <v>1.16588567328164</v>
+        <v>1.184167960309155</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.76473096858151</v>
+        <v>4.653923271637755</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2343137929092406</v>
+        <v>0.2339691133883152</v>
       </c>
       <c r="C45">
-        <v>444.9397007329934</v>
+        <v>441.5255417903473</v>
       </c>
       <c r="D45">
-        <v>621.1757007329934</v>
+        <v>622.3135417903474</v>
       </c>
       <c r="E45">
-        <v>-68.16399999999999</v>
+        <v>-63.61199999999999</v>
       </c>
       <c r="F45">
-        <v>195.736</v>
+        <v>200.288</v>
       </c>
       <c r="G45">
         <v>19.5</v>
@@ -5081,28 +5081,28 @@
         <v>50.375</v>
       </c>
       <c r="M45">
-        <v>10.8242008</v>
+        <v>11.0759264</v>
       </c>
       <c r="N45">
-        <v>39.5507992</v>
+        <v>39.2990736</v>
       </c>
       <c r="O45">
-        <v>6.723635864</v>
+        <v>6.680842512000001</v>
       </c>
       <c r="P45">
-        <v>32.827163336</v>
+        <v>32.618231088</v>
       </c>
       <c r="Q45">
-        <v>33.827163336</v>
+        <v>33.618231088</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3764512682618255</v>
+        <v>0.38173848819342</v>
       </c>
       <c r="T45">
-        <v>1.184167960309155</v>
+        <v>1.203103186159081</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.653923271637755</v>
+        <v>4.548152288191442</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5127,22 +5127,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2339691133883152</v>
+        <v>0.2345581838673898</v>
       </c>
       <c r="C46">
-        <v>441.5255417903473</v>
+        <v>435.0314456719899</v>
       </c>
       <c r="D46">
-        <v>622.3135417903474</v>
+        <v>620.3714456719899</v>
       </c>
       <c r="E46">
-        <v>-63.61199999999999</v>
+        <v>-59.05999999999997</v>
       </c>
       <c r="F46">
-        <v>200.288</v>
+        <v>204.84</v>
       </c>
       <c r="G46">
         <v>19.5</v>
@@ -5163,45 +5163,45 @@
         <v>50.375</v>
       </c>
       <c r="M46">
-        <v>11.0759264</v>
+        <v>11.839752</v>
       </c>
       <c r="N46">
-        <v>39.2990736</v>
+        <v>38.535248</v>
       </c>
       <c r="O46">
-        <v>6.680842512000001</v>
+        <v>6.55099216</v>
       </c>
       <c r="P46">
-        <v>32.618231088</v>
+        <v>31.98425584</v>
       </c>
       <c r="Q46">
-        <v>33.618231088</v>
+        <v>32.98425584</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.38173848819342</v>
+        <v>0.3872179706679815</v>
       </c>
       <c r="T46">
-        <v>1.203103186159081</v>
+        <v>1.222726965676276</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.17</v>
       </c>
       <c r="W46">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.548152288191442</v>
+        <v>4.254734389706811</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5209,22 +5209,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2345581838673898</v>
+        <v>0.2342342543464645</v>
       </c>
       <c r="C47">
-        <v>435.0314456719899</v>
+        <v>431.5459005259083</v>
       </c>
       <c r="D47">
-        <v>620.3714456719899</v>
+        <v>621.4379005259083</v>
       </c>
       <c r="E47">
-        <v>-59.05999999999997</v>
+        <v>-54.50799999999998</v>
       </c>
       <c r="F47">
-        <v>204.84</v>
+        <v>209.392</v>
       </c>
       <c r="G47">
         <v>19.5</v>
@@ -5245,28 +5245,28 @@
         <v>50.375</v>
       </c>
       <c r="M47">
-        <v>11.839752</v>
+        <v>12.1028576</v>
       </c>
       <c r="N47">
-        <v>38.535248</v>
+        <v>38.2721424</v>
       </c>
       <c r="O47">
-        <v>6.55099216</v>
+        <v>6.506264208</v>
       </c>
       <c r="P47">
-        <v>31.98425584</v>
+        <v>31.765878192</v>
       </c>
       <c r="Q47">
-        <v>32.98425584</v>
+        <v>32.765878192</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3872179706679815</v>
+        <v>0.3929003969378972</v>
       </c>
       <c r="T47">
-        <v>1.222726965676276</v>
+        <v>1.243077551842258</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.254734389706811</v>
+        <v>4.16224016384362</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5291,22 +5291,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2342342543464645</v>
+        <v>0.2339103248255391</v>
       </c>
       <c r="C48">
-        <v>431.5459005259083</v>
+        <v>428.0640282905002</v>
       </c>
       <c r="D48">
-        <v>621.4379005259083</v>
+        <v>622.5080282905002</v>
       </c>
       <c r="E48">
-        <v>-54.50799999999998</v>
+        <v>-49.95599999999996</v>
       </c>
       <c r="F48">
-        <v>209.392</v>
+        <v>213.944</v>
       </c>
       <c r="G48">
         <v>19.5</v>
@@ -5327,28 +5327,28 @@
         <v>50.375</v>
       </c>
       <c r="M48">
-        <v>12.1028576</v>
+        <v>12.3659632</v>
       </c>
       <c r="N48">
-        <v>38.2721424</v>
+        <v>38.0090368</v>
       </c>
       <c r="O48">
-        <v>6.506264208</v>
+        <v>6.461536256</v>
       </c>
       <c r="P48">
-        <v>31.765878192</v>
+        <v>31.547500544</v>
       </c>
       <c r="Q48">
-        <v>32.765878192</v>
+        <v>32.547500544</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3929003969378972</v>
+        <v>0.3987972543878097</v>
       </c>
       <c r="T48">
-        <v>1.243077551842258</v>
+        <v>1.264196084656012</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.16224016384362</v>
+        <v>4.073681862485245</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5373,22 +5373,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2339103248255391</v>
+        <v>0.2349807953046138</v>
       </c>
       <c r="C49">
-        <v>428.0640282905002</v>
+        <v>419.9895963956615</v>
       </c>
       <c r="D49">
-        <v>622.5080282905002</v>
+        <v>618.9855963956614</v>
       </c>
       <c r="E49">
-        <v>-49.95599999999996</v>
+        <v>-45.40399999999997</v>
       </c>
       <c r="F49">
-        <v>213.944</v>
+        <v>218.496</v>
       </c>
       <c r="G49">
         <v>19.5</v>
@@ -5409,45 +5409,45 @@
         <v>50.375</v>
       </c>
       <c r="M49">
-        <v>12.3659632</v>
+        <v>13.3938048</v>
       </c>
       <c r="N49">
-        <v>38.0090368</v>
+        <v>36.9811952</v>
       </c>
       <c r="O49">
-        <v>6.461536256</v>
+        <v>6.286803184000001</v>
       </c>
       <c r="P49">
-        <v>31.547500544</v>
+        <v>30.694392016</v>
       </c>
       <c r="Q49">
-        <v>32.547500544</v>
+        <v>31.694392016</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3987972543878097</v>
+        <v>0.4049209140473342</v>
       </c>
       <c r="T49">
-        <v>1.264196084656012</v>
+        <v>1.286126868731833</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.17</v>
       </c>
       <c r="W49">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.073681862485245</v>
+        <v>3.761067206235528</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5455,22 +5455,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2349807953046137</v>
+        <v>0.2346859157836884</v>
       </c>
       <c r="C50">
-        <v>419.9895963956616</v>
+        <v>416.4039266557423</v>
       </c>
       <c r="D50">
-        <v>618.9855963956616</v>
+        <v>619.9519266557423</v>
       </c>
       <c r="E50">
-        <v>-45.404</v>
+        <v>-40.85199999999998</v>
       </c>
       <c r="F50">
-        <v>218.496</v>
+        <v>223.048</v>
       </c>
       <c r="G50">
         <v>19.5</v>
@@ -5491,28 +5491,28 @@
         <v>50.375</v>
       </c>
       <c r="M50">
-        <v>13.3938048</v>
+        <v>13.6728424</v>
       </c>
       <c r="N50">
-        <v>36.9811952</v>
+        <v>36.7021576</v>
       </c>
       <c r="O50">
-        <v>6.286803184000001</v>
+        <v>6.239366792</v>
       </c>
       <c r="P50">
-        <v>30.694392016</v>
+        <v>30.462790808</v>
       </c>
       <c r="Q50">
-        <v>31.694392016</v>
+        <v>31.462790808</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.4049209140473342</v>
+        <v>0.4112847172229184</v>
       </c>
       <c r="T50">
-        <v>1.286126868731833</v>
+        <v>1.308917683555726</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.761067206235528</v>
+        <v>3.684310732638884</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5537,22 +5537,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2346859157836884</v>
+        <v>0.2343910362627631</v>
       </c>
       <c r="C51">
-        <v>416.4039266557423</v>
+        <v>412.8212788092256</v>
       </c>
       <c r="D51">
-        <v>619.9519266557423</v>
+        <v>620.9212788092257</v>
       </c>
       <c r="E51">
-        <v>-40.85199999999998</v>
+        <v>-36.29999999999998</v>
       </c>
       <c r="F51">
-        <v>223.048</v>
+        <v>227.6</v>
       </c>
       <c r="G51">
         <v>19.5</v>
@@ -5573,28 +5573,28 @@
         <v>50.375</v>
       </c>
       <c r="M51">
-        <v>13.6728424</v>
+        <v>13.95188</v>
       </c>
       <c r="N51">
-        <v>36.7021576</v>
+        <v>36.42312</v>
       </c>
       <c r="O51">
-        <v>6.239366792</v>
+        <v>6.1919304</v>
       </c>
       <c r="P51">
-        <v>30.462790808</v>
+        <v>30.2311896</v>
       </c>
       <c r="Q51">
-        <v>31.462790808</v>
+        <v>31.2311896</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.4112847172229184</v>
+        <v>0.4179030725255262</v>
       </c>
       <c r="T51">
-        <v>1.308917683555726</v>
+        <v>1.332620130972574</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.684310732638884</v>
+        <v>3.610624517986107</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5619,22 +5619,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2343910362627631</v>
+        <v>0.2340961567418377</v>
       </c>
       <c r="C52">
-        <v>412.8212788092256</v>
+        <v>409.2416670533398</v>
       </c>
       <c r="D52">
-        <v>620.9212788092257</v>
+        <v>621.8936670533398</v>
       </c>
       <c r="E52">
-        <v>-36.29999999999998</v>
+        <v>-31.74799999999999</v>
       </c>
       <c r="F52">
-        <v>227.6</v>
+        <v>232.152</v>
       </c>
       <c r="G52">
         <v>19.5</v>
@@ -5655,28 +5655,28 @@
         <v>50.375</v>
       </c>
       <c r="M52">
-        <v>13.95188</v>
+        <v>14.2309176</v>
       </c>
       <c r="N52">
-        <v>36.42312</v>
+        <v>36.1440824</v>
       </c>
       <c r="O52">
-        <v>6.1919304</v>
+        <v>6.144494008000001</v>
       </c>
       <c r="P52">
-        <v>30.2311896</v>
+        <v>29.999588392</v>
       </c>
       <c r="Q52">
-        <v>31.2311896</v>
+        <v>30.999588392</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.4179030725255262</v>
+        <v>0.4247915647792607</v>
       </c>
       <c r="T52">
-        <v>1.332620130972574</v>
+        <v>1.357290025222764</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.610624517986107</v>
+        <v>3.539827958809909</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5701,22 +5701,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2340961567418377</v>
+        <v>0.2350097572209124</v>
       </c>
       <c r="C53">
-        <v>409.2416670533398</v>
+        <v>401.6868496484737</v>
       </c>
       <c r="D53">
-        <v>621.8936670533398</v>
+        <v>618.8908496484737</v>
       </c>
       <c r="E53">
-        <v>-31.74799999999999</v>
+        <v>-27.19599999999997</v>
       </c>
       <c r="F53">
-        <v>232.152</v>
+        <v>236.704</v>
       </c>
       <c r="G53">
         <v>19.5</v>
@@ -5737,45 +5737,45 @@
         <v>50.375</v>
       </c>
       <c r="M53">
-        <v>14.2309176</v>
+        <v>15.1727264</v>
       </c>
       <c r="N53">
-        <v>36.1440824</v>
+        <v>35.2022736</v>
       </c>
       <c r="O53">
-        <v>6.144494008000001</v>
+        <v>5.984386512</v>
       </c>
       <c r="P53">
-        <v>29.999588392</v>
+        <v>29.217887088</v>
       </c>
       <c r="Q53">
-        <v>30.999588392</v>
+        <v>30.217887088</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.4247915647792607</v>
+        <v>0.4319670775435675</v>
       </c>
       <c r="T53">
-        <v>1.357290025222764</v>
+        <v>1.382987831733378</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.17</v>
       </c>
       <c r="W53">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.539827958809909</v>
+        <v>3.320102048370159</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5783,22 +5783,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2350097572209124</v>
+        <v>0.234738117699987</v>
       </c>
       <c r="C54">
-        <v>401.6868496484737</v>
+        <v>398.0246394693427</v>
       </c>
       <c r="D54">
-        <v>618.8908496484737</v>
+        <v>619.7806394693426</v>
       </c>
       <c r="E54">
-        <v>-27.19599999999997</v>
+        <v>-22.64399999999998</v>
       </c>
       <c r="F54">
-        <v>236.704</v>
+        <v>241.256</v>
       </c>
       <c r="G54">
         <v>19.5</v>
@@ -5819,28 +5819,28 @@
         <v>50.375</v>
       </c>
       <c r="M54">
-        <v>15.1727264</v>
+        <v>15.4645096</v>
       </c>
       <c r="N54">
-        <v>35.2022736</v>
+        <v>34.9104904</v>
       </c>
       <c r="O54">
-        <v>5.984386512</v>
+        <v>5.934783368000001</v>
       </c>
       <c r="P54">
-        <v>29.217887088</v>
+        <v>28.975707032</v>
       </c>
       <c r="Q54">
-        <v>30.217887088</v>
+        <v>29.975707032</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.4319670775435675</v>
+        <v>0.4394479312765682</v>
       </c>
       <c r="T54">
-        <v>1.382987831733378</v>
+        <v>1.409779161925294</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.320102048370159</v>
+        <v>3.257458613495251</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5865,22 +5865,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.234738117699987</v>
+        <v>0.2344664781790617</v>
       </c>
       <c r="C55">
-        <v>398.0246394693427</v>
+        <v>394.3649915056408</v>
       </c>
       <c r="D55">
-        <v>619.7806394693426</v>
+        <v>620.6729915056408</v>
       </c>
       <c r="E55">
-        <v>-22.64399999999998</v>
+        <v>-18.09199999999996</v>
       </c>
       <c r="F55">
-        <v>241.256</v>
+        <v>245.808</v>
       </c>
       <c r="G55">
         <v>19.5</v>
@@ -5901,28 +5901,28 @@
         <v>50.375</v>
       </c>
       <c r="M55">
-        <v>15.4645096</v>
+        <v>15.7562928</v>
       </c>
       <c r="N55">
-        <v>34.9104904</v>
+        <v>34.6187072</v>
       </c>
       <c r="O55">
-        <v>5.934783368000001</v>
+        <v>5.885180224</v>
       </c>
       <c r="P55">
-        <v>28.975707032</v>
+        <v>28.733526976</v>
       </c>
       <c r="Q55">
-        <v>29.975707032</v>
+        <v>29.733526976</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.4394479312765682</v>
+        <v>0.4472540395196993</v>
       </c>
       <c r="T55">
-        <v>1.409779161925294</v>
+        <v>1.437735332560337</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.257458613495251</v>
+        <v>3.197135305837931</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5947,22 +5947,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2344664781790617</v>
+        <v>0.2341948386581363</v>
       </c>
       <c r="C56">
-        <v>394.3649915056408</v>
+        <v>390.7079168404576</v>
       </c>
       <c r="D56">
-        <v>620.6729915056408</v>
+        <v>621.5679168404577</v>
       </c>
       <c r="E56">
-        <v>-18.09199999999996</v>
+        <v>-13.53999999999996</v>
       </c>
       <c r="F56">
-        <v>245.808</v>
+        <v>250.36</v>
       </c>
       <c r="G56">
         <v>19.5</v>
@@ -5983,28 +5983,28 @@
         <v>50.375</v>
       </c>
       <c r="M56">
-        <v>15.7562928</v>
+        <v>16.048076</v>
       </c>
       <c r="N56">
-        <v>34.6187072</v>
+        <v>34.326924</v>
       </c>
       <c r="O56">
-        <v>5.885180224</v>
+        <v>5.83557708</v>
       </c>
       <c r="P56">
-        <v>28.733526976</v>
+        <v>28.49134692</v>
       </c>
       <c r="Q56">
-        <v>29.733526976</v>
+        <v>29.49134692</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.4472540395196993</v>
+        <v>0.4554070859069697</v>
       </c>
       <c r="T56">
-        <v>1.437735332560337</v>
+        <v>1.46693399966805</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.197135305837931</v>
+        <v>3.139005573004515</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6029,22 +6029,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2341948386581363</v>
+        <v>0.2339231991372109</v>
       </c>
       <c r="C57">
-        <v>390.7079168404576</v>
+        <v>387.0534266208966</v>
       </c>
       <c r="D57">
-        <v>621.5679168404577</v>
+        <v>622.4654266208967</v>
       </c>
       <c r="E57">
-        <v>-13.53999999999996</v>
+        <v>-8.987999999999971</v>
       </c>
       <c r="F57">
-        <v>250.36</v>
+        <v>254.912</v>
       </c>
       <c r="G57">
         <v>19.5</v>
@@ -6065,28 +6065,28 @@
         <v>50.375</v>
       </c>
       <c r="M57">
-        <v>16.048076</v>
+        <v>16.3398592</v>
       </c>
       <c r="N57">
-        <v>34.326924</v>
+        <v>34.03514079999999</v>
       </c>
       <c r="O57">
-        <v>5.83557708</v>
+        <v>5.785973936</v>
       </c>
       <c r="P57">
-        <v>28.49134692</v>
+        <v>28.249166864</v>
       </c>
       <c r="Q57">
-        <v>29.49134692</v>
+        <v>29.249166864</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.4554070859069697</v>
+        <v>0.4639307253118431</v>
       </c>
       <c r="T57">
-        <v>1.46693399966805</v>
+        <v>1.497459878917021</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.139005573004515</v>
+        <v>3.082951902058005</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2339231991372109</v>
+        <v>0.2336515596162856</v>
       </c>
       <c r="C58">
-        <v>387.0534266208966</v>
+        <v>383.4015320585372</v>
       </c>
       <c r="D58">
-        <v>622.4654266208967</v>
+        <v>623.3655320585372</v>
       </c>
       <c r="E58">
-        <v>-8.987999999999971</v>
+        <v>-4.435999999999979</v>
       </c>
       <c r="F58">
-        <v>254.912</v>
+        <v>259.464</v>
       </c>
       <c r="G58">
         <v>19.5</v>
@@ -6147,28 +6147,28 @@
         <v>50.375</v>
       </c>
       <c r="M58">
-        <v>16.3398592</v>
+        <v>16.6316424</v>
       </c>
       <c r="N58">
-        <v>34.03514079999999</v>
+        <v>33.7433576</v>
       </c>
       <c r="O58">
-        <v>5.785973936</v>
+        <v>5.736370792</v>
       </c>
       <c r="P58">
-        <v>28.249166864</v>
+        <v>28.006986808</v>
       </c>
       <c r="Q58">
-        <v>29.249166864</v>
+        <v>29.006986808</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4639307253118431</v>
+        <v>0.4728508130611294</v>
       </c>
       <c r="T58">
-        <v>1.497459878917021</v>
+        <v>1.529405566503154</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.082951902058005</v>
+        <v>3.028865026583303</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6193,22 +6193,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2336515596162856</v>
+        <v>0.2371348400953602</v>
       </c>
       <c r="C59">
-        <v>383.4015320585372</v>
+        <v>367.5010657360146</v>
       </c>
       <c r="D59">
-        <v>623.3655320585372</v>
+        <v>612.0170657360146</v>
       </c>
       <c r="E59">
-        <v>-4.435999999999979</v>
+        <v>0.1160000000000423</v>
       </c>
       <c r="F59">
-        <v>259.464</v>
+        <v>264.016</v>
       </c>
       <c r="G59">
         <v>19.5</v>
@@ -6229,45 +6229,45 @@
         <v>50.375</v>
       </c>
       <c r="M59">
-        <v>16.6316424</v>
+        <v>18.9827504</v>
       </c>
       <c r="N59">
-        <v>33.7433576</v>
+        <v>31.3922496</v>
       </c>
       <c r="O59">
-        <v>5.736370792</v>
+        <v>5.336682432</v>
       </c>
       <c r="P59">
-        <v>28.006986808</v>
+        <v>26.055567168</v>
       </c>
       <c r="Q59">
-        <v>29.006986808</v>
+        <v>27.055567168</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4728508130611294</v>
+        <v>0.4821956668937148</v>
       </c>
       <c r="T59">
-        <v>1.529405566503154</v>
+        <v>1.562872477307674</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.17</v>
       </c>
       <c r="W59">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.028865026583303</v>
+        <v>2.653725036599543</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6275,22 +6275,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2371348400953602</v>
+        <v>0.2369279405744349</v>
       </c>
       <c r="C60">
-        <v>367.5010657360144</v>
+        <v>363.611585498004</v>
       </c>
       <c r="D60">
-        <v>612.0170657360144</v>
+        <v>612.679585498004</v>
       </c>
       <c r="E60">
-        <v>0.1159999999999854</v>
+        <v>4.668000000000006</v>
       </c>
       <c r="F60">
-        <v>264.016</v>
+        <v>268.568</v>
       </c>
       <c r="G60">
         <v>19.5</v>
@@ -6311,28 +6311,28 @@
         <v>50.375</v>
       </c>
       <c r="M60">
-        <v>18.9827504</v>
+        <v>19.3100392</v>
       </c>
       <c r="N60">
-        <v>31.3922496</v>
+        <v>31.0649608</v>
       </c>
       <c r="O60">
-        <v>5.336682432</v>
+        <v>5.281043336</v>
       </c>
       <c r="P60">
-        <v>26.055567168</v>
+        <v>25.783917464</v>
       </c>
       <c r="Q60">
-        <v>27.055567168</v>
+        <v>26.783917464</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4821956668937148</v>
+        <v>0.4919963672547192</v>
       </c>
       <c r="T60">
-        <v>1.562872477307674</v>
+        <v>1.597971920346561</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.653725036599544</v>
+        <v>2.608746646148703</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6357,22 +6357,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2369279405744349</v>
+        <v>0.2367210410535095</v>
       </c>
       <c r="C61">
-        <v>363.611585498004</v>
+        <v>359.7235411941432</v>
       </c>
       <c r="D61">
-        <v>612.679585498004</v>
+        <v>613.3435411941432</v>
       </c>
       <c r="E61">
-        <v>4.668000000000006</v>
+        <v>9.220000000000027</v>
       </c>
       <c r="F61">
-        <v>268.568</v>
+        <v>273.12</v>
       </c>
       <c r="G61">
         <v>19.5</v>
@@ -6393,28 +6393,28 @@
         <v>50.375</v>
       </c>
       <c r="M61">
-        <v>19.3100392</v>
+        <v>19.637328</v>
       </c>
       <c r="N61">
-        <v>31.0649608</v>
+        <v>30.737672</v>
       </c>
       <c r="O61">
-        <v>5.281043336</v>
+        <v>5.22540424</v>
       </c>
       <c r="P61">
-        <v>25.783917464</v>
+        <v>25.51226776</v>
       </c>
       <c r="Q61">
-        <v>26.783917464</v>
+        <v>26.51226776</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4919963672547192</v>
+        <v>0.5022871026337737</v>
       </c>
       <c r="T61">
-        <v>1.597971920346561</v>
+        <v>1.634826335537393</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.608746646148703</v>
+        <v>2.565267535379559</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6439,22 +6439,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2367210410535095</v>
+        <v>0.2365141415325842</v>
       </c>
       <c r="C62">
-        <v>359.7235411941432</v>
+        <v>355.8369374978253</v>
       </c>
       <c r="D62">
-        <v>613.3435411941432</v>
+        <v>614.0089374978253</v>
       </c>
       <c r="E62">
-        <v>9.220000000000027</v>
+        <v>13.77199999999999</v>
       </c>
       <c r="F62">
-        <v>273.12</v>
+        <v>277.672</v>
       </c>
       <c r="G62">
         <v>19.5</v>
@@ -6475,28 +6475,28 @@
         <v>50.375</v>
       </c>
       <c r="M62">
-        <v>19.637328</v>
+        <v>19.9646168</v>
       </c>
       <c r="N62">
-        <v>30.737672</v>
+        <v>30.4103832</v>
       </c>
       <c r="O62">
-        <v>5.22540424</v>
+        <v>5.169765144</v>
       </c>
       <c r="P62">
-        <v>25.51226776</v>
+        <v>25.240618056</v>
       </c>
       <c r="Q62">
-        <v>26.51226776</v>
+        <v>26.240618056</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.5022871026337737</v>
+        <v>0.5131055680322671</v>
       </c>
       <c r="T62">
-        <v>1.634826335537393</v>
+        <v>1.673570720738011</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.565267535379559</v>
+        <v>2.523213969225796</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6521,22 +6521,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2365141415325842</v>
+        <v>0.2383141820116588</v>
       </c>
       <c r="C63">
-        <v>355.8369374978253</v>
+        <v>345.5438490727516</v>
       </c>
       <c r="D63">
-        <v>614.0089374978253</v>
+        <v>608.2678490727516</v>
       </c>
       <c r="E63">
-        <v>13.77199999999999</v>
+        <v>18.32400000000001</v>
       </c>
       <c r="F63">
-        <v>277.672</v>
+        <v>282.224</v>
       </c>
       <c r="G63">
         <v>19.5</v>
@@ -6557,45 +6557,45 @@
         <v>50.375</v>
       </c>
       <c r="M63">
-        <v>19.9646168</v>
+        <v>21.3925792</v>
       </c>
       <c r="N63">
-        <v>30.4103832</v>
+        <v>28.9824208</v>
       </c>
       <c r="O63">
-        <v>5.169765144</v>
+        <v>4.927011536</v>
       </c>
       <c r="P63">
-        <v>25.240618056</v>
+        <v>24.055409264</v>
       </c>
       <c r="Q63">
-        <v>26.240618056</v>
+        <v>25.055409264</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.5131055680322671</v>
+        <v>0.5244934263464706</v>
       </c>
       <c r="T63">
-        <v>1.673570720738011</v>
+        <v>1.714354284107082</v>
       </c>
       <c r="U63">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.17</v>
       </c>
       <c r="W63">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.523213969225796</v>
+        <v>2.354788524050433</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6603,22 +6603,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2383141820116588</v>
+        <v>0.2381396524907334</v>
       </c>
       <c r="C64">
-        <v>345.5438490727516</v>
+        <v>341.5437929642905</v>
       </c>
       <c r="D64">
-        <v>608.2678490727516</v>
+        <v>608.8197929642905</v>
       </c>
       <c r="E64">
-        <v>18.32400000000001</v>
+        <v>22.87600000000003</v>
       </c>
       <c r="F64">
-        <v>282.224</v>
+        <v>286.776</v>
       </c>
       <c r="G64">
         <v>19.5</v>
@@ -6639,28 +6639,28 @@
         <v>50.375</v>
       </c>
       <c r="M64">
-        <v>21.3925792</v>
+        <v>21.7376208</v>
       </c>
       <c r="N64">
-        <v>28.9824208</v>
+        <v>28.6373792</v>
       </c>
       <c r="O64">
-        <v>4.927011536</v>
+        <v>4.868354464</v>
       </c>
       <c r="P64">
-        <v>24.055409264</v>
+        <v>23.769024736</v>
       </c>
       <c r="Q64">
-        <v>25.055409264</v>
+        <v>24.769024736</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.5244934263464706</v>
+        <v>0.5364968445695498</v>
       </c>
       <c r="T64">
-        <v>1.714354284107082</v>
+        <v>1.757342364415022</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.354788524050433</v>
+        <v>2.317410928430585</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6685,22 +6685,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2381396524907334</v>
+        <v>0.2379651229698081</v>
       </c>
       <c r="C65">
-        <v>341.5437929642905</v>
+        <v>337.5447394363338</v>
       </c>
       <c r="D65">
-        <v>608.8197929642905</v>
+        <v>609.3727394363337</v>
       </c>
       <c r="E65">
-        <v>22.87600000000003</v>
+        <v>27.428</v>
       </c>
       <c r="F65">
-        <v>286.776</v>
+        <v>291.328</v>
       </c>
       <c r="G65">
         <v>19.5</v>
@@ -6721,28 +6721,28 @@
         <v>50.375</v>
       </c>
       <c r="M65">
-        <v>21.7376208</v>
+        <v>22.0826624</v>
       </c>
       <c r="N65">
-        <v>28.6373792</v>
+        <v>28.2923376</v>
       </c>
       <c r="O65">
-        <v>4.868354464</v>
+        <v>4.809697392</v>
       </c>
       <c r="P65">
-        <v>23.769024736</v>
+        <v>23.482640208</v>
       </c>
       <c r="Q65">
-        <v>24.769024736</v>
+        <v>24.482640208</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.5364968445695498</v>
+        <v>0.549167119360578</v>
       </c>
       <c r="T65">
-        <v>1.757342364415022</v>
+        <v>1.802718671406737</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.317410928430585</v>
+        <v>2.281201382673857</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6767,22 +6767,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2379651229698081</v>
+        <v>0.2377905934488828</v>
       </c>
       <c r="C66">
-        <v>337.5447394363338</v>
+        <v>333.5466912230762</v>
       </c>
       <c r="D66">
-        <v>609.3727394363337</v>
+        <v>609.9266912230762</v>
       </c>
       <c r="E66">
-        <v>27.428</v>
+        <v>31.98000000000002</v>
       </c>
       <c r="F66">
-        <v>291.328</v>
+        <v>295.88</v>
       </c>
       <c r="G66">
         <v>19.5</v>
@@ -6803,28 +6803,28 @@
         <v>50.375</v>
       </c>
       <c r="M66">
-        <v>22.0826624</v>
+        <v>22.427704</v>
       </c>
       <c r="N66">
-        <v>28.2923376</v>
+        <v>27.947296</v>
       </c>
       <c r="O66">
-        <v>4.809697392</v>
+        <v>4.75104032</v>
       </c>
       <c r="P66">
-        <v>23.482640208</v>
+        <v>23.19625568</v>
       </c>
       <c r="Q66">
-        <v>24.482640208</v>
+        <v>24.19625568</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.549167119360578</v>
+        <v>0.5625614098539509</v>
       </c>
       <c r="T66">
-        <v>1.802718671406737</v>
+        <v>1.85068791022655</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.281201382673857</v>
+        <v>2.246105976786567</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6849,22 +6849,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2377905934488828</v>
+        <v>0.2376160639279574</v>
       </c>
       <c r="C67">
-        <v>333.5466912230762</v>
+        <v>329.5496510686643</v>
       </c>
       <c r="D67">
-        <v>609.9266912230762</v>
+        <v>610.4816510686643</v>
       </c>
       <c r="E67">
-        <v>31.98000000000002</v>
+        <v>36.53200000000004</v>
       </c>
       <c r="F67">
-        <v>295.88</v>
+        <v>300.432</v>
       </c>
       <c r="G67">
         <v>19.5</v>
@@ -6885,28 +6885,28 @@
         <v>50.375</v>
       </c>
       <c r="M67">
-        <v>22.427704</v>
+        <v>22.7727456</v>
       </c>
       <c r="N67">
-        <v>27.947296</v>
+        <v>27.6022544</v>
       </c>
       <c r="O67">
-        <v>4.75104032</v>
+        <v>4.692383248</v>
       </c>
       <c r="P67">
-        <v>23.19625568</v>
+        <v>22.909871152</v>
       </c>
       <c r="Q67">
-        <v>24.19625568</v>
+        <v>23.909871152</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5625614098539509</v>
+        <v>0.5767435997881101</v>
       </c>
       <c r="T67">
-        <v>1.85068791022655</v>
+        <v>1.901478868976939</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.246105976786567</v>
+        <v>2.212074068047376</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6931,22 +6931,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2376160639279574</v>
+        <v>0.2374415344070321</v>
       </c>
       <c r="C68">
-        <v>329.5496510686643</v>
+        <v>325.5536217272399</v>
       </c>
       <c r="D68">
-        <v>610.4816510686643</v>
+        <v>611.03762172724</v>
       </c>
       <c r="E68">
-        <v>36.53200000000004</v>
+        <v>41.08400000000006</v>
       </c>
       <c r="F68">
-        <v>300.432</v>
+        <v>304.984</v>
       </c>
       <c r="G68">
         <v>19.5</v>
@@ -6967,28 +6967,28 @@
         <v>50.375</v>
       </c>
       <c r="M68">
-        <v>22.7727456</v>
+        <v>23.11778720000001</v>
       </c>
       <c r="N68">
-        <v>27.6022544</v>
+        <v>27.25721279999999</v>
       </c>
       <c r="O68">
-        <v>4.692383248</v>
+        <v>4.633726176</v>
       </c>
       <c r="P68">
-        <v>22.909871152</v>
+        <v>22.62348662399999</v>
       </c>
       <c r="Q68">
-        <v>23.909871152</v>
+        <v>23.62348662399999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.5767435997881101</v>
+        <v>0.5917853163849457</v>
       </c>
       <c r="T68">
-        <v>1.901478868976939</v>
+        <v>1.955348067651595</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.212074068047376</v>
+        <v>2.179058037180997</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7013,22 +7013,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2374415344070321</v>
+        <v>0.2372670048861067</v>
       </c>
       <c r="C69">
-        <v>325.5536217272399</v>
+        <v>321.558605962988</v>
       </c>
       <c r="D69">
-        <v>611.03762172724</v>
+        <v>611.594605962988</v>
       </c>
       <c r="E69">
-        <v>41.08400000000006</v>
+        <v>45.63600000000002</v>
       </c>
       <c r="F69">
-        <v>304.984</v>
+        <v>309.536</v>
       </c>
       <c r="G69">
         <v>19.5</v>
@@ -7049,28 +7049,28 @@
         <v>50.375</v>
       </c>
       <c r="M69">
-        <v>23.11778720000001</v>
+        <v>23.4628288</v>
       </c>
       <c r="N69">
-        <v>27.25721279999999</v>
+        <v>26.9121712</v>
       </c>
       <c r="O69">
-        <v>4.633726176</v>
+        <v>4.575069104000001</v>
       </c>
       <c r="P69">
-        <v>22.62348662399999</v>
+        <v>22.337102096</v>
       </c>
       <c r="Q69">
-        <v>23.62348662399999</v>
+        <v>23.337102096</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5917853163849457</v>
+        <v>0.6077671402690835</v>
       </c>
       <c r="T69">
-        <v>1.955348067651595</v>
+        <v>2.012584091243417</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.179058037180997</v>
+        <v>2.147013066045983</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7095,22 +7095,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2372670048861067</v>
+        <v>0.2370924753651814</v>
       </c>
       <c r="C70">
-        <v>321.558605962988</v>
+        <v>317.5646065501803</v>
       </c>
       <c r="D70">
-        <v>611.594605962988</v>
+        <v>612.1526065501803</v>
       </c>
       <c r="E70">
-        <v>45.63600000000002</v>
+        <v>50.18800000000005</v>
       </c>
       <c r="F70">
-        <v>309.536</v>
+        <v>314.088</v>
       </c>
       <c r="G70">
         <v>19.5</v>
@@ -7131,28 +7131,28 @@
         <v>50.375</v>
       </c>
       <c r="M70">
-        <v>23.4628288</v>
+        <v>23.8078704</v>
       </c>
       <c r="N70">
-        <v>26.9121712</v>
+        <v>26.5671296</v>
       </c>
       <c r="O70">
-        <v>4.575069104000001</v>
+        <v>4.516412032</v>
       </c>
       <c r="P70">
-        <v>22.337102096</v>
+        <v>22.050717568</v>
       </c>
       <c r="Q70">
-        <v>23.337102096</v>
+        <v>23.050717568</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.6077671402690835</v>
+        <v>0.6247800495651012</v>
       </c>
       <c r="T70">
-        <v>2.012584091243417</v>
+        <v>2.073512761518582</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.147013066045983</v>
+        <v>2.115896934654012</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7177,22 +7177,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2370924753651814</v>
+        <v>0.236917945844256</v>
       </c>
       <c r="C71">
-        <v>317.5646065501803</v>
+        <v>313.5716262732232</v>
       </c>
       <c r="D71">
-        <v>612.1526065501803</v>
+        <v>612.7116262732233</v>
       </c>
       <c r="E71">
-        <v>50.18800000000005</v>
+        <v>54.74000000000007</v>
       </c>
       <c r="F71">
-        <v>314.088</v>
+        <v>318.64</v>
       </c>
       <c r="G71">
         <v>19.5</v>
@@ -7213,28 +7213,28 @@
         <v>50.375</v>
       </c>
       <c r="M71">
-        <v>23.8078704</v>
+        <v>24.152912</v>
       </c>
       <c r="N71">
-        <v>26.5671296</v>
+        <v>26.222088</v>
       </c>
       <c r="O71">
-        <v>4.516412032</v>
+        <v>4.45775496</v>
       </c>
       <c r="P71">
-        <v>22.050717568</v>
+        <v>21.76433304</v>
       </c>
       <c r="Q71">
-        <v>23.050717568</v>
+        <v>22.76433304</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.6247800495651012</v>
+        <v>0.6429271528141868</v>
       </c>
       <c r="T71">
-        <v>2.073512761518582</v>
+        <v>2.138503343145425</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.115896934654012</v>
+        <v>2.085669835587526</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7259,22 +7259,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.236917945844256</v>
+        <v>0.2367434163233306</v>
       </c>
       <c r="C72">
-        <v>313.5716262732232</v>
+        <v>309.5796679267035</v>
       </c>
       <c r="D72">
-        <v>612.7116262732233</v>
+        <v>613.2716679267035</v>
       </c>
       <c r="E72">
-        <v>54.74000000000007</v>
+        <v>59.29200000000003</v>
       </c>
       <c r="F72">
-        <v>318.64</v>
+        <v>323.192</v>
       </c>
       <c r="G72">
         <v>19.5</v>
@@ -7295,28 +7295,28 @@
         <v>50.375</v>
       </c>
       <c r="M72">
-        <v>24.152912</v>
+        <v>24.4979536</v>
       </c>
       <c r="N72">
-        <v>26.222088</v>
+        <v>25.8770464</v>
       </c>
       <c r="O72">
-        <v>4.45775496</v>
+        <v>4.399097888</v>
       </c>
       <c r="P72">
-        <v>21.76433304</v>
+        <v>21.477948512</v>
       </c>
       <c r="Q72">
-        <v>22.76433304</v>
+        <v>22.477948512</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.6429271528141868</v>
+        <v>0.6623257804252782</v>
       </c>
       <c r="T72">
-        <v>2.138503343145425</v>
+        <v>2.207976033849981</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.085669835587526</v>
+        <v>2.056294204100378</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7341,22 +7341,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2367434163233306</v>
+        <v>0.2365688868024053</v>
       </c>
       <c r="C73">
-        <v>309.5796679267035</v>
+        <v>305.5887343154338</v>
       </c>
       <c r="D73">
-        <v>613.2716679267035</v>
+        <v>613.8327343154338</v>
       </c>
       <c r="E73">
-        <v>59.29199999999997</v>
+        <v>63.84399999999999</v>
       </c>
       <c r="F73">
-        <v>323.192</v>
+        <v>327.744</v>
       </c>
       <c r="G73">
         <v>19.5</v>
@@ -7377,28 +7377,28 @@
         <v>50.375</v>
       </c>
       <c r="M73">
-        <v>24.4979536</v>
+        <v>24.8429952</v>
       </c>
       <c r="N73">
-        <v>25.8770464</v>
+        <v>25.5320048</v>
       </c>
       <c r="O73">
-        <v>4.399097888000001</v>
+        <v>4.340440816</v>
       </c>
       <c r="P73">
-        <v>21.477948512</v>
+        <v>21.191563984</v>
       </c>
       <c r="Q73">
-        <v>22.477948512</v>
+        <v>22.191563984</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.662325780425278</v>
+        <v>0.6831100242943046</v>
       </c>
       <c r="T73">
-        <v>2.20797603384998</v>
+        <v>2.282411059604862</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.056294204100379</v>
+        <v>2.027734562376762</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7423,22 +7423,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2365688868024053</v>
+        <v>0.2449981372814799</v>
       </c>
       <c r="C74">
-        <v>305.5887343154338</v>
+        <v>275.0618434835549</v>
       </c>
       <c r="D74">
-        <v>613.8327343154338</v>
+        <v>587.8578434835549</v>
       </c>
       <c r="E74">
-        <v>63.84399999999999</v>
+        <v>68.39600000000002</v>
       </c>
       <c r="F74">
-        <v>327.744</v>
+        <v>332.296</v>
       </c>
       <c r="G74">
         <v>19.5</v>
@@ -7459,45 +7459,45 @@
         <v>50.375</v>
       </c>
       <c r="M74">
-        <v>24.8429952</v>
+        <v>29.90664</v>
       </c>
       <c r="N74">
-        <v>25.5320048</v>
+        <v>20.46836</v>
       </c>
       <c r="O74">
-        <v>4.340440816</v>
+        <v>3.4796212</v>
       </c>
       <c r="P74">
-        <v>21.191563984</v>
+        <v>16.9887388</v>
       </c>
       <c r="Q74">
-        <v>22.191563984</v>
+        <v>17.9887388</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.6831100242943046</v>
+        <v>0.705433841783259</v>
       </c>
       <c r="T74">
-        <v>2.282411059604862</v>
+        <v>2.362359790971216</v>
       </c>
       <c r="U74">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V74">
         <v>0.17</v>
       </c>
       <c r="W74">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.027734562376762</v>
+        <v>1.684408546062012</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7505,22 +7505,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2449981372814799</v>
+        <v>0.2449414677605546</v>
       </c>
       <c r="C75">
-        <v>275.0618434835549</v>
+        <v>270.6771296984103</v>
       </c>
       <c r="D75">
-        <v>587.8578434835549</v>
+        <v>588.0251296984103</v>
       </c>
       <c r="E75">
-        <v>68.39600000000002</v>
+        <v>72.94800000000004</v>
       </c>
       <c r="F75">
-        <v>332.296</v>
+        <v>336.848</v>
       </c>
       <c r="G75">
         <v>19.5</v>
@@ -7541,28 +7541,28 @@
         <v>50.375</v>
       </c>
       <c r="M75">
-        <v>29.90664</v>
+        <v>30.31632</v>
       </c>
       <c r="N75">
-        <v>20.46836</v>
+        <v>20.05868</v>
       </c>
       <c r="O75">
-        <v>3.4796212</v>
+        <v>3.4099756</v>
       </c>
       <c r="P75">
-        <v>16.9887388</v>
+        <v>16.6487044</v>
       </c>
       <c r="Q75">
-        <v>17.9887388</v>
+        <v>17.6487044</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.705433841783259</v>
+        <v>0.729474876002133</v>
       </c>
       <c r="T75">
-        <v>2.362359790971216</v>
+        <v>2.448458424750366</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.684408546062012</v>
+        <v>1.661646268412525</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7587,22 +7587,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2449414677605546</v>
+        <v>0.2448847982396292</v>
       </c>
       <c r="C76">
-        <v>270.6771296984103</v>
+        <v>266.2925111493636</v>
       </c>
       <c r="D76">
-        <v>588.0251296984103</v>
+        <v>588.1925111493636</v>
       </c>
       <c r="E76">
-        <v>72.94800000000004</v>
+        <v>77.5</v>
       </c>
       <c r="F76">
-        <v>336.848</v>
+        <v>341.4</v>
       </c>
       <c r="G76">
         <v>19.5</v>
@@ -7623,28 +7623,28 @@
         <v>50.375</v>
       </c>
       <c r="M76">
-        <v>30.31632</v>
+        <v>30.726</v>
       </c>
       <c r="N76">
-        <v>20.05868</v>
+        <v>19.649</v>
       </c>
       <c r="O76">
-        <v>3.4099756</v>
+        <v>3.340330000000001</v>
       </c>
       <c r="P76">
-        <v>16.6487044</v>
+        <v>16.30867</v>
       </c>
       <c r="Q76">
-        <v>17.6487044</v>
+        <v>17.30867</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.729474876002133</v>
+        <v>0.755439192958517</v>
       </c>
       <c r="T76">
-        <v>2.448458424750366</v>
+        <v>2.541444949231849</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.661646268412525</v>
+        <v>1.639490984833692</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7669,22 +7669,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2448847982396292</v>
+        <v>0.2448281287187039</v>
       </c>
       <c r="C77">
-        <v>266.2925111493636</v>
+        <v>261.9079879177646</v>
       </c>
       <c r="D77">
-        <v>588.1925111493636</v>
+        <v>588.3599879177646</v>
       </c>
       <c r="E77">
-        <v>77.5</v>
+        <v>82.05200000000002</v>
       </c>
       <c r="F77">
-        <v>341.4</v>
+        <v>345.952</v>
       </c>
       <c r="G77">
         <v>19.5</v>
@@ -7705,28 +7705,28 @@
         <v>50.375</v>
       </c>
       <c r="M77">
-        <v>30.726</v>
+        <v>31.13568</v>
       </c>
       <c r="N77">
-        <v>19.649</v>
+        <v>19.23932</v>
       </c>
       <c r="O77">
-        <v>3.340330000000001</v>
+        <v>3.270684400000001</v>
       </c>
       <c r="P77">
-        <v>16.30867</v>
+        <v>15.9686356</v>
       </c>
       <c r="Q77">
-        <v>17.30867</v>
+        <v>16.9686356</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.755439192958517</v>
+        <v>0.7835672029945996</v>
       </c>
       <c r="T77">
-        <v>2.541444949231849</v>
+        <v>2.642180350753456</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.639490984833692</v>
+        <v>1.617918735033248</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7751,22 +7751,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2448281287187039</v>
+        <v>0.2447714591977785</v>
       </c>
       <c r="C78">
-        <v>261.9079879177646</v>
+        <v>257.5235600850563</v>
       </c>
       <c r="D78">
-        <v>588.3599879177646</v>
+        <v>588.5275600850563</v>
       </c>
       <c r="E78">
-        <v>82.05200000000002</v>
+        <v>86.60400000000004</v>
       </c>
       <c r="F78">
-        <v>345.952</v>
+        <v>350.504</v>
       </c>
       <c r="G78">
         <v>19.5</v>
@@ -7787,28 +7787,28 @@
         <v>50.375</v>
       </c>
       <c r="M78">
-        <v>31.13568</v>
+        <v>31.54536</v>
       </c>
       <c r="N78">
-        <v>19.23932</v>
+        <v>18.82964</v>
       </c>
       <c r="O78">
-        <v>3.270684400000001</v>
+        <v>3.2010388</v>
       </c>
       <c r="P78">
-        <v>15.9686356</v>
+        <v>15.6286012</v>
       </c>
       <c r="Q78">
-        <v>16.9686356</v>
+        <v>16.6286012</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.7835672029945996</v>
+        <v>0.8141411269468632</v>
       </c>
       <c r="T78">
-        <v>2.642180350753456</v>
+        <v>2.751675352407375</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.617918735033248</v>
+        <v>1.59690680340944</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7833,22 +7833,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2447714591977785</v>
+        <v>0.2447147896768532</v>
       </c>
       <c r="C79">
-        <v>257.5235600850563</v>
+        <v>253.1392277327739</v>
       </c>
       <c r="D79">
-        <v>588.5275600850563</v>
+        <v>588.6952277327739</v>
       </c>
       <c r="E79">
-        <v>86.60400000000004</v>
+        <v>91.15600000000001</v>
       </c>
       <c r="F79">
-        <v>350.504</v>
+        <v>355.056</v>
       </c>
       <c r="G79">
         <v>19.5</v>
@@ -7869,28 +7869,28 @@
         <v>50.375</v>
       </c>
       <c r="M79">
-        <v>31.54536</v>
+        <v>31.95504</v>
       </c>
       <c r="N79">
-        <v>18.82964</v>
+        <v>18.41996</v>
       </c>
       <c r="O79">
-        <v>3.2010388</v>
+        <v>3.131393200000001</v>
       </c>
       <c r="P79">
-        <v>15.6286012</v>
+        <v>15.2885668</v>
       </c>
       <c r="Q79">
-        <v>16.6286012</v>
+        <v>16.2885668</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.8141411269468632</v>
+        <v>0.847494498531151</v>
       </c>
       <c r="T79">
-        <v>2.751675352407375</v>
+        <v>2.871124445120743</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.59690680340944</v>
+        <v>1.576433639263165</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7915,22 +7915,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2447147896768532</v>
+        <v>0.2446581201559278</v>
       </c>
       <c r="C80">
-        <v>253.1392277327739</v>
+        <v>248.7549909425464</v>
       </c>
       <c r="D80">
-        <v>588.6952277327739</v>
+        <v>588.8629909425464</v>
       </c>
       <c r="E80">
-        <v>91.15600000000001</v>
+        <v>95.70800000000003</v>
       </c>
       <c r="F80">
-        <v>355.056</v>
+        <v>359.608</v>
       </c>
       <c r="G80">
         <v>19.5</v>
@@ -7951,28 +7951,28 @@
         <v>50.375</v>
       </c>
       <c r="M80">
-        <v>31.95504</v>
+        <v>32.36472</v>
       </c>
       <c r="N80">
-        <v>18.41996</v>
+        <v>18.01028</v>
       </c>
       <c r="O80">
-        <v>3.131393200000001</v>
+        <v>3.0617476</v>
       </c>
       <c r="P80">
-        <v>15.2885668</v>
+        <v>14.9485324</v>
       </c>
       <c r="Q80">
-        <v>16.2885668</v>
+        <v>15.9485324</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.847494498531151</v>
+        <v>0.8840243816948945</v>
       </c>
       <c r="T80">
-        <v>2.871124445120743</v>
+        <v>3.001949641902049</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.576433639263165</v>
+        <v>1.55647878306996</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7997,22 +7997,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2446581201559278</v>
+        <v>0.2446014506350024</v>
       </c>
       <c r="C81">
-        <v>248.7549909425464</v>
+        <v>244.3708497960949</v>
       </c>
       <c r="D81">
-        <v>588.8629909425464</v>
+        <v>589.0308497960949</v>
       </c>
       <c r="E81">
-        <v>95.70800000000003</v>
+        <v>100.26</v>
       </c>
       <c r="F81">
-        <v>359.608</v>
+        <v>364.16</v>
       </c>
       <c r="G81">
         <v>19.5</v>
@@ -8033,28 +8033,28 @@
         <v>50.375</v>
       </c>
       <c r="M81">
-        <v>32.36472</v>
+        <v>32.7744</v>
       </c>
       <c r="N81">
-        <v>18.01028</v>
+        <v>17.6006</v>
       </c>
       <c r="O81">
-        <v>3.0617476</v>
+        <v>2.992102</v>
       </c>
       <c r="P81">
-        <v>14.9485324</v>
+        <v>14.608498</v>
       </c>
       <c r="Q81">
-        <v>15.9485324</v>
+        <v>15.608498</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.8840243816948945</v>
+        <v>0.9242072531750125</v>
       </c>
       <c r="T81">
-        <v>3.001949641902049</v>
+        <v>3.145857358361487</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.55647878306996</v>
+        <v>1.537022798281586</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8079,22 +8079,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2446014506350024</v>
+        <v>0.2445447811140771</v>
       </c>
       <c r="C82">
-        <v>244.3708497960949</v>
+        <v>239.9868043752344</v>
       </c>
       <c r="D82">
-        <v>589.0308497960949</v>
+        <v>589.1988043752344</v>
       </c>
       <c r="E82">
-        <v>100.26</v>
+        <v>104.812</v>
       </c>
       <c r="F82">
-        <v>364.16</v>
+        <v>368.712</v>
       </c>
       <c r="G82">
         <v>19.5</v>
@@ -8115,28 +8115,28 @@
         <v>50.375</v>
       </c>
       <c r="M82">
-        <v>32.7744</v>
+        <v>33.18407999999999</v>
       </c>
       <c r="N82">
-        <v>17.6006</v>
+        <v>17.19092000000001</v>
       </c>
       <c r="O82">
-        <v>2.992102</v>
+        <v>2.922456400000001</v>
       </c>
       <c r="P82">
-        <v>14.608498</v>
+        <v>14.2684636</v>
       </c>
       <c r="Q82">
-        <v>15.608498</v>
+        <v>15.2684636</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.9242072531750125</v>
+        <v>0.9686199006004063</v>
       </c>
       <c r="T82">
-        <v>3.145857358361487</v>
+        <v>3.304913255500866</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.537022798281586</v>
+        <v>1.518047208179344</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8161,22 +8161,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2445447811140771</v>
+        <v>0.2870834477594261</v>
       </c>
       <c r="C83">
-        <v>239.9868043752344</v>
+        <v>131.5580910743438</v>
       </c>
       <c r="D83">
-        <v>589.1988043752344</v>
+        <v>485.3220910743439</v>
       </c>
       <c r="E83">
-        <v>104.812</v>
+        <v>109.364</v>
       </c>
       <c r="F83">
-        <v>368.712</v>
+        <v>373.264</v>
       </c>
       <c r="G83">
         <v>19.5</v>
@@ -8197,45 +8197,45 @@
         <v>50.375</v>
       </c>
       <c r="M83">
-        <v>33.18407999999999</v>
+        <v>54.7951552</v>
       </c>
       <c r="N83">
-        <v>17.19092000000001</v>
+        <v>-4.420155200000004</v>
       </c>
       <c r="O83">
-        <v>2.922456400000001</v>
+        <v>-0.7514263840000006</v>
       </c>
       <c r="P83">
-        <v>14.2684636</v>
+        <v>-3.668728816000003</v>
       </c>
       <c r="Q83">
-        <v>15.2684636</v>
+        <v>-2.668728816000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.9686199006004063</v>
+        <v>1.030670037835515</v>
       </c>
       <c r="T83">
-        <v>3.304913255500866</v>
+        <v>3.527134645525655</v>
       </c>
       <c r="U83">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.17</v>
+        <v>0.1562866273257676</v>
       </c>
       <c r="W83">
-        <v>0.07469999999999999</v>
+        <v>0.1238571231085773</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.518047208179344</v>
+        <v>0.9193331019162803</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8243,22 +8243,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2870834477594261</v>
+        <v>0.2880934477594262</v>
       </c>
       <c r="C84">
-        <v>131.5580910743438</v>
+        <v>124.9830264123898</v>
       </c>
       <c r="D84">
-        <v>485.3220910743439</v>
+        <v>483.2990264123898</v>
       </c>
       <c r="E84">
-        <v>109.364</v>
+        <v>113.9160000000001</v>
       </c>
       <c r="F84">
-        <v>373.264</v>
+        <v>377.816</v>
       </c>
       <c r="G84">
         <v>19.5</v>
@@ -8279,37 +8279,37 @@
         <v>50.375</v>
       </c>
       <c r="M84">
-        <v>54.7951552</v>
+        <v>55.46338880000001</v>
       </c>
       <c r="N84">
-        <v>-4.420155200000004</v>
+        <v>-5.088388800000011</v>
       </c>
       <c r="O84">
-        <v>-0.7514263840000006</v>
+        <v>-0.865026096000002</v>
       </c>
       <c r="P84">
-        <v>-3.668728816000003</v>
+        <v>-4.223362704000009</v>
       </c>
       <c r="Q84">
-        <v>-2.668728816000003</v>
+        <v>-3.223362704000009</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>1.030670037835515</v>
+        <v>1.088603569472899</v>
       </c>
       <c r="T84">
-        <v>3.527134645525655</v>
+        <v>3.734613154085989</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1562866273257676</v>
+        <v>0.1544036559122042</v>
       </c>
       <c r="W84">
-        <v>0.1238571231085773</v>
+        <v>0.1241335433120884</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9193331019162803</v>
+        <v>0.9082567994835539</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8325,22 +8325,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2880934477594262</v>
+        <v>0.2891034477594262</v>
       </c>
       <c r="C85">
-        <v>124.9830264123898</v>
+        <v>118.4247580213262</v>
       </c>
       <c r="D85">
-        <v>483.2990264123898</v>
+        <v>481.2927580213262</v>
       </c>
       <c r="E85">
-        <v>113.9160000000001</v>
+        <v>118.4680000000001</v>
       </c>
       <c r="F85">
-        <v>377.816</v>
+        <v>382.3680000000001</v>
       </c>
       <c r="G85">
         <v>19.5</v>
@@ -8361,37 +8361,37 @@
         <v>50.375</v>
       </c>
       <c r="M85">
-        <v>55.46338880000001</v>
+        <v>56.13162240000001</v>
       </c>
       <c r="N85">
-        <v>-5.088388800000011</v>
+        <v>-5.756622400000012</v>
       </c>
       <c r="O85">
-        <v>-0.865026096000002</v>
+        <v>-0.9786258080000021</v>
       </c>
       <c r="P85">
-        <v>-4.223362704000009</v>
+        <v>-4.77799659200001</v>
       </c>
       <c r="Q85">
-        <v>-3.223362704000009</v>
+        <v>-3.77799659200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>1.088603569472899</v>
+        <v>1.153778792564955</v>
       </c>
       <c r="T85">
-        <v>3.734613154085989</v>
+        <v>3.968026476216364</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1544036559122042</v>
+        <v>0.1525655171513446</v>
       </c>
       <c r="W85">
-        <v>0.1241335433120884</v>
+        <v>0.1244033820821826</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9082567994835539</v>
+        <v>0.8974442185373211</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8407,22 +8407,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2891034477594261</v>
+        <v>0.2901134477594262</v>
       </c>
       <c r="C86">
-        <v>118.4247580213263</v>
+        <v>111.8830775921091</v>
       </c>
       <c r="D86">
-        <v>481.2927580213263</v>
+        <v>479.303077592109</v>
       </c>
       <c r="E86">
-        <v>118.468</v>
+        <v>123.02</v>
       </c>
       <c r="F86">
-        <v>382.368</v>
+        <v>386.92</v>
       </c>
       <c r="G86">
         <v>19.5</v>
@@ -8443,37 +8443,37 @@
         <v>50.375</v>
       </c>
       <c r="M86">
-        <v>56.1316224</v>
+        <v>56.799856</v>
       </c>
       <c r="N86">
-        <v>-5.756622400000005</v>
+        <v>-6.424855999999998</v>
       </c>
       <c r="O86">
-        <v>-0.9786258080000009</v>
+        <v>-1.09222552</v>
       </c>
       <c r="P86">
-        <v>-4.777996592000004</v>
+        <v>-5.332630479999999</v>
       </c>
       <c r="Q86">
-        <v>-3.777996592000004</v>
+        <v>-4.332630479999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.153778792564955</v>
+        <v>1.227644045402618</v>
       </c>
       <c r="T86">
-        <v>3.968026476216361</v>
+        <v>4.232561574630785</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1525655171513446</v>
+        <v>0.15077062871427</v>
       </c>
       <c r="W86">
-        <v>0.1244033820821826</v>
+        <v>0.1246668717047452</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8974442185373213</v>
+        <v>0.8868860512604116</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8489,22 +8489,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2901134477594262</v>
+        <v>0.2911234477594261</v>
       </c>
       <c r="C87">
-        <v>111.8830775921091</v>
+        <v>105.3577802461385</v>
       </c>
       <c r="D87">
-        <v>479.303077592109</v>
+        <v>477.3297802461385</v>
       </c>
       <c r="E87">
-        <v>123.02</v>
+        <v>127.572</v>
       </c>
       <c r="F87">
-        <v>386.92</v>
+        <v>391.472</v>
       </c>
       <c r="G87">
         <v>19.5</v>
@@ -8525,37 +8525,37 @@
         <v>50.375</v>
       </c>
       <c r="M87">
-        <v>56.799856</v>
+        <v>57.4680896</v>
       </c>
       <c r="N87">
-        <v>-6.424855999999998</v>
+        <v>-7.093089599999999</v>
       </c>
       <c r="O87">
-        <v>-1.09222552</v>
+        <v>-1.205825232</v>
       </c>
       <c r="P87">
-        <v>-5.332630479999999</v>
+        <v>-5.887264367999999</v>
       </c>
       <c r="Q87">
-        <v>-4.332630479999999</v>
+        <v>-4.887264367999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.227644045402618</v>
+        <v>1.312061477217091</v>
       </c>
       <c r="T87">
-        <v>4.232561574630785</v>
+        <v>4.534887401390127</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.15077062871427</v>
+        <v>0.1490174818687552</v>
       </c>
       <c r="W87">
-        <v>0.1246668717047452</v>
+        <v>0.1249242336616667</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8868860512604116</v>
+        <v>0.8765734227573836</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8571,22 +8571,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2911234477594261</v>
+        <v>0.2921334477594262</v>
       </c>
       <c r="C88">
-        <v>105.3577802461385</v>
+        <v>98.84866446493339</v>
       </c>
       <c r="D88">
-        <v>477.3297802461385</v>
+        <v>475.3726644649334</v>
       </c>
       <c r="E88">
-        <v>127.572</v>
+        <v>132.124</v>
       </c>
       <c r="F88">
-        <v>391.472</v>
+        <v>396.024</v>
       </c>
       <c r="G88">
         <v>19.5</v>
@@ -8607,37 +8607,37 @@
         <v>50.375</v>
       </c>
       <c r="M88">
-        <v>57.4680896</v>
+        <v>58.13632320000001</v>
       </c>
       <c r="N88">
-        <v>-7.093089599999999</v>
+        <v>-7.761323200000007</v>
       </c>
       <c r="O88">
-        <v>-1.205825232</v>
+        <v>-1.319424944000001</v>
       </c>
       <c r="P88">
-        <v>-5.887264367999999</v>
+        <v>-6.441898256000005</v>
       </c>
       <c r="Q88">
-        <v>-4.887264367999999</v>
+        <v>-5.441898256000005</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.312061477217091</v>
+        <v>1.40946620623379</v>
       </c>
       <c r="T88">
-        <v>4.534887401390127</v>
+        <v>4.883724893804753</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1490174818687552</v>
+        <v>0.1473046372495741</v>
       </c>
       <c r="W88">
-        <v>0.1249242336616667</v>
+        <v>0.1251756792517625</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8765734227573836</v>
+        <v>0.8664978661739653</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8653,22 +8653,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2921334477594262</v>
+        <v>0.2931434477594261</v>
       </c>
       <c r="C89">
-        <v>98.84866446493339</v>
+        <v>92.35553202152806</v>
       </c>
       <c r="D89">
-        <v>475.3726644649334</v>
+        <v>473.431532021528</v>
       </c>
       <c r="E89">
-        <v>132.124</v>
+        <v>136.676</v>
       </c>
       <c r="F89">
-        <v>396.024</v>
+        <v>400.576</v>
       </c>
       <c r="G89">
         <v>19.5</v>
@@ -8689,37 +8689,37 @@
         <v>50.375</v>
       </c>
       <c r="M89">
-        <v>58.13632320000001</v>
+        <v>58.8045568</v>
       </c>
       <c r="N89">
-        <v>-7.761323200000007</v>
+        <v>-8.4295568</v>
       </c>
       <c r="O89">
-        <v>-1.319424944000001</v>
+        <v>-1.433024656</v>
       </c>
       <c r="P89">
-        <v>-6.441898256000005</v>
+        <v>-6.996532144</v>
       </c>
       <c r="Q89">
-        <v>-5.441898256000005</v>
+        <v>-5.996532144</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.40946620623379</v>
+        <v>1.523105056753273</v>
       </c>
       <c r="T89">
-        <v>4.883724893804753</v>
+        <v>5.290701968288483</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1473046372495741</v>
+        <v>0.1456307209171926</v>
       </c>
       <c r="W89">
-        <v>0.1251756792517625</v>
+        <v>0.1254214101693561</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8664978661739653</v>
+        <v>0.8566512995128976</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8735,22 +8735,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2931434477594261</v>
+        <v>0.2941534477594261</v>
       </c>
       <c r="C90">
-        <v>92.35553202152806</v>
+        <v>85.87818791354152</v>
       </c>
       <c r="D90">
-        <v>473.431532021528</v>
+        <v>471.5061879135415</v>
       </c>
       <c r="E90">
-        <v>136.676</v>
+        <v>141.228</v>
       </c>
       <c r="F90">
-        <v>400.576</v>
+        <v>405.128</v>
       </c>
       <c r="G90">
         <v>19.5</v>
@@ -8771,37 +8771,37 @@
         <v>50.375</v>
       </c>
       <c r="M90">
-        <v>58.8045568</v>
+        <v>59.4727904</v>
       </c>
       <c r="N90">
-        <v>-8.4295568</v>
+        <v>-9.097790400000001</v>
       </c>
       <c r="O90">
-        <v>-1.433024656</v>
+        <v>-1.546624368</v>
       </c>
       <c r="P90">
-        <v>-6.996532144</v>
+        <v>-7.551166032000001</v>
       </c>
       <c r="Q90">
-        <v>-5.996532144</v>
+        <v>-6.551166032000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.523105056753273</v>
+        <v>1.657405516458116</v>
       </c>
       <c r="T90">
-        <v>5.290701968288483</v>
+        <v>5.771674874496527</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1456307209171926</v>
+        <v>0.1439944206821679</v>
       </c>
       <c r="W90">
-        <v>0.1254214101693561</v>
+        <v>0.1256616190438578</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8566512995128976</v>
+        <v>0.8470260040127526</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8817,22 +8817,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2941534477594261</v>
+        <v>0.2951634477594262</v>
       </c>
       <c r="C91">
-        <v>85.87818791354152</v>
+        <v>79.41644029787608</v>
       </c>
       <c r="D91">
-        <v>471.5061879135415</v>
+        <v>469.5964402978761</v>
       </c>
       <c r="E91">
-        <v>141.228</v>
+        <v>145.78</v>
       </c>
       <c r="F91">
-        <v>405.128</v>
+        <v>409.68</v>
       </c>
       <c r="G91">
         <v>19.5</v>
@@ -8853,37 +8853,37 @@
         <v>50.375</v>
       </c>
       <c r="M91">
-        <v>59.4727904</v>
+        <v>60.14102400000001</v>
       </c>
       <c r="N91">
-        <v>-9.097790400000001</v>
+        <v>-9.766024000000009</v>
       </c>
       <c r="O91">
-        <v>-1.546624368</v>
+        <v>-1.660224080000002</v>
       </c>
       <c r="P91">
-        <v>-7.551166032000001</v>
+        <v>-8.105799920000006</v>
       </c>
       <c r="Q91">
-        <v>-6.551166032000001</v>
+        <v>-7.105799920000006</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.657405516458116</v>
+        <v>1.818566068103928</v>
       </c>
       <c r="T91">
-        <v>5.771674874496527</v>
+        <v>6.34884236194618</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1439944206821679</v>
+        <v>0.1423944826745883</v>
       </c>
       <c r="W91">
-        <v>0.1256616190438578</v>
+        <v>0.1258964899433704</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8470260040127526</v>
+        <v>0.8376146039681664</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8899,22 +8899,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2951634477594262</v>
+        <v>0.2961734477594261</v>
       </c>
       <c r="C92">
-        <v>79.41644029787608</v>
+        <v>72.97010042699418</v>
       </c>
       <c r="D92">
-        <v>469.5964402978761</v>
+        <v>467.7021004269942</v>
       </c>
       <c r="E92">
-        <v>145.78</v>
+        <v>150.3320000000001</v>
       </c>
       <c r="F92">
-        <v>409.68</v>
+        <v>414.232</v>
       </c>
       <c r="G92">
         <v>19.5</v>
@@ -8935,37 +8935,37 @@
         <v>50.375</v>
       </c>
       <c r="M92">
-        <v>60.14102400000001</v>
+        <v>60.80925760000001</v>
       </c>
       <c r="N92">
-        <v>-9.766024000000009</v>
+        <v>-10.43425760000001</v>
       </c>
       <c r="O92">
-        <v>-1.660224080000002</v>
+        <v>-1.773823792000002</v>
       </c>
       <c r="P92">
-        <v>-8.105799920000006</v>
+        <v>-8.660433808000008</v>
       </c>
       <c r="Q92">
-        <v>-7.105799920000006</v>
+        <v>-7.660433808000008</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.818566068103928</v>
+        <v>2.015540075671031</v>
       </c>
       <c r="T92">
-        <v>6.34884236194618</v>
+        <v>7.054269291051312</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1423944826745883</v>
+        <v>0.1408297081397027</v>
       </c>
       <c r="W92">
-        <v>0.1258964899433704</v>
+        <v>0.1261261988450917</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8376146039681664</v>
+        <v>0.8284100478806041</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8981,22 +8981,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2961734477594261</v>
+        <v>0.2971834477594262</v>
       </c>
       <c r="C93">
-        <v>72.97010042699418</v>
+        <v>66.53898258673223</v>
       </c>
       <c r="D93">
-        <v>467.7021004269942</v>
+        <v>465.8229825867322</v>
       </c>
       <c r="E93">
-        <v>150.3320000000001</v>
+        <v>154.884</v>
       </c>
       <c r="F93">
-        <v>414.232</v>
+        <v>418.784</v>
       </c>
       <c r="G93">
         <v>19.5</v>
@@ -9017,37 +9017,37 @@
         <v>50.375</v>
       </c>
       <c r="M93">
-        <v>60.80925760000001</v>
+        <v>61.4774912</v>
       </c>
       <c r="N93">
-        <v>-10.43425760000001</v>
+        <v>-11.1024912</v>
       </c>
       <c r="O93">
-        <v>-1.773823792000002</v>
+        <v>-1.887423504000001</v>
       </c>
       <c r="P93">
-        <v>-8.660433808000008</v>
+        <v>-9.215067696000002</v>
       </c>
       <c r="Q93">
-        <v>-7.660433808000008</v>
+        <v>-8.215067696000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>2.015540075671031</v>
+        <v>2.261757585129911</v>
       </c>
       <c r="T93">
-        <v>7.054269291051312</v>
+        <v>7.936052952432727</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1408297081397027</v>
+        <v>0.139298950442532</v>
       </c>
       <c r="W93">
-        <v>0.1261261988450917</v>
+        <v>0.1263509140750363</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8284100478806041</v>
+        <v>0.8194055908384238</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9063,22 +9063,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2971834477594262</v>
+        <v>0.2981934477594262</v>
       </c>
       <c r="C94">
-        <v>66.53898258673223</v>
+        <v>60.12290403560814</v>
       </c>
       <c r="D94">
-        <v>465.8229825867322</v>
+        <v>463.9589040356082</v>
       </c>
       <c r="E94">
-        <v>154.884</v>
+        <v>159.436</v>
       </c>
       <c r="F94">
-        <v>418.784</v>
+        <v>423.336</v>
       </c>
       <c r="G94">
         <v>19.5</v>
@@ -9099,37 +9099,37 @@
         <v>50.375</v>
       </c>
       <c r="M94">
-        <v>61.4774912</v>
+        <v>62.14572480000001</v>
       </c>
       <c r="N94">
-        <v>-11.1024912</v>
+        <v>-11.77072480000001</v>
       </c>
       <c r="O94">
-        <v>-1.887423504000001</v>
+        <v>-2.001023216000002</v>
       </c>
       <c r="P94">
-        <v>-9.215067696000002</v>
+        <v>-9.769701584000009</v>
       </c>
       <c r="Q94">
-        <v>-8.215067696000002</v>
+        <v>-8.769701584000009</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.261757585129911</v>
+        <v>2.578322954434184</v>
       </c>
       <c r="T94">
-        <v>7.936052952432727</v>
+        <v>9.069774802780262</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.139298950442532</v>
+        <v>0.1378011122657306</v>
       </c>
       <c r="W94">
-        <v>0.1263509140750363</v>
+        <v>0.1265707967193908</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8194055908384238</v>
+        <v>0.8105947780337095</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9145,22 +9145,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2981934477594262</v>
+        <v>0.2992034477594261</v>
       </c>
       <c r="C95">
-        <v>60.12290403560814</v>
+        <v>53.72168494557894</v>
       </c>
       <c r="D95">
-        <v>463.9589040356082</v>
+        <v>462.109684945579</v>
       </c>
       <c r="E95">
-        <v>159.436</v>
+        <v>163.9880000000001</v>
       </c>
       <c r="F95">
-        <v>423.336</v>
+        <v>427.888</v>
       </c>
       <c r="G95">
         <v>19.5</v>
@@ -9181,37 +9181,37 @@
         <v>50.375</v>
       </c>
       <c r="M95">
-        <v>62.14572480000001</v>
+        <v>62.81395840000001</v>
       </c>
       <c r="N95">
-        <v>-11.77072480000001</v>
+        <v>-12.43895840000001</v>
       </c>
       <c r="O95">
-        <v>-2.001023216000002</v>
+        <v>-2.114622928000002</v>
       </c>
       <c r="P95">
-        <v>-9.769701584000009</v>
+        <v>-10.32433547200001</v>
       </c>
       <c r="Q95">
-        <v>-8.769701584000009</v>
+        <v>-9.324335472000008</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.578322954434184</v>
+        <v>3.000410113506548</v>
       </c>
       <c r="T95">
-        <v>9.069774802780262</v>
+        <v>10.58140393657697</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1378011122657306</v>
+        <v>0.1363351429863079</v>
       </c>
       <c r="W95">
-        <v>0.1265707967193908</v>
+        <v>0.12678600100961</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8105947780337095</v>
+        <v>0.8019714293312231</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9227,22 +9227,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2992034477594261</v>
+        <v>0.3585211862899363</v>
       </c>
       <c r="C96">
-        <v>53.72168494557894</v>
+        <v>-38.48443849012637</v>
       </c>
       <c r="D96">
-        <v>462.109684945579</v>
+        <v>374.4555615098736</v>
       </c>
       <c r="E96">
-        <v>163.9880000000001</v>
+        <v>168.54</v>
       </c>
       <c r="F96">
-        <v>427.888</v>
+        <v>432.44</v>
       </c>
       <c r="G96">
         <v>19.5</v>
@@ -9263,45 +9263,45 @@
         <v>50.375</v>
       </c>
       <c r="M96">
-        <v>62.81395840000001</v>
+        <v>86.833952</v>
       </c>
       <c r="N96">
-        <v>-12.43895840000001</v>
+        <v>-36.458952</v>
       </c>
       <c r="O96">
-        <v>-2.114622928000002</v>
+        <v>-6.19802184</v>
       </c>
       <c r="P96">
-        <v>-10.32433547200001</v>
+        <v>-30.26093016</v>
       </c>
       <c r="Q96">
-        <v>-9.324335472000008</v>
+        <v>-29.26093016</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>3.000410113506548</v>
+        <v>3.731486906818064</v>
       </c>
       <c r="T96">
-        <v>10.58140393657697</v>
+        <v>13.19962379012835</v>
       </c>
       <c r="U96">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1363351429863079</v>
+        <v>0.09862213803190716</v>
       </c>
       <c r="W96">
-        <v>0.12678600100961</v>
+        <v>0.1809966746831931</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.8019714293312231</v>
+        <v>0.5801302237171009</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9309,22 +9309,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3585211862899363</v>
+        <v>0.3600711862899363</v>
       </c>
       <c r="C97">
-        <v>-38.48443849012637</v>
+        <v>-44.88327060729301</v>
       </c>
       <c r="D97">
-        <v>374.4555615098736</v>
+        <v>372.608729392707</v>
       </c>
       <c r="E97">
-        <v>168.54</v>
+        <v>173.092</v>
       </c>
       <c r="F97">
-        <v>432.44</v>
+        <v>436.992</v>
       </c>
       <c r="G97">
         <v>19.5</v>
@@ -9345,37 +9345,37 @@
         <v>50.375</v>
       </c>
       <c r="M97">
-        <v>86.833952</v>
+        <v>87.7479936</v>
       </c>
       <c r="N97">
-        <v>-36.458952</v>
+        <v>-37.3729936</v>
       </c>
       <c r="O97">
-        <v>-6.19802184</v>
+        <v>-6.353408912000001</v>
       </c>
       <c r="P97">
-        <v>-30.26093016</v>
+        <v>-31.019584688</v>
       </c>
       <c r="Q97">
-        <v>-29.26093016</v>
+        <v>-30.019584688</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.731486906818064</v>
+        <v>4.652908633522582</v>
       </c>
       <c r="T97">
-        <v>13.19962379012835</v>
+        <v>16.49952973766045</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09862213803190716</v>
+        <v>0.09759482409407479</v>
       </c>
       <c r="W97">
-        <v>0.1809966746831931</v>
+        <v>0.1812029593219098</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5801302237171009</v>
+        <v>0.574087200553381</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9391,22 +9391,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3600711862899363</v>
+        <v>0.3616211862899363</v>
       </c>
       <c r="C98">
-        <v>-44.88327060729296</v>
+        <v>-51.26397480964022</v>
       </c>
       <c r="D98">
-        <v>372.608729392707</v>
+        <v>370.7800251903598</v>
       </c>
       <c r="E98">
-        <v>173.092</v>
+        <v>177.644</v>
       </c>
       <c r="F98">
-        <v>436.992</v>
+        <v>441.544</v>
       </c>
       <c r="G98">
         <v>19.5</v>
@@ -9427,37 +9427,37 @@
         <v>50.375</v>
       </c>
       <c r="M98">
-        <v>87.7479936</v>
+        <v>88.66203520000001</v>
       </c>
       <c r="N98">
-        <v>-37.3729936</v>
+        <v>-38.28703520000001</v>
       </c>
       <c r="O98">
-        <v>-6.353408912000001</v>
+        <v>-6.508795984000002</v>
       </c>
       <c r="P98">
-        <v>-31.019584688</v>
+        <v>-31.778239216</v>
       </c>
       <c r="Q98">
-        <v>-30.019584688</v>
+        <v>-30.778239216</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.65290863352257</v>
+        <v>6.188611511363426</v>
       </c>
       <c r="T98">
-        <v>16.49952973766041</v>
+        <v>21.99937298354721</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09759482409407479</v>
+        <v>0.09658869188691938</v>
       </c>
       <c r="W98">
-        <v>0.1812029593219098</v>
+        <v>0.1814049906691066</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.574087200553381</v>
+        <v>0.568168775805408</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9473,22 +9473,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3616211862899363</v>
+        <v>0.3631711862899364</v>
       </c>
       <c r="C99">
-        <v>-51.26397480964022</v>
+        <v>-57.62681670037205</v>
       </c>
       <c r="D99">
-        <v>370.7800251903598</v>
+        <v>368.969183299628</v>
       </c>
       <c r="E99">
-        <v>177.644</v>
+        <v>182.196</v>
       </c>
       <c r="F99">
-        <v>441.544</v>
+        <v>446.096</v>
       </c>
       <c r="G99">
         <v>19.5</v>
@@ -9509,37 +9509,37 @@
         <v>50.375</v>
       </c>
       <c r="M99">
-        <v>88.66203520000001</v>
+        <v>89.57607680000001</v>
       </c>
       <c r="N99">
-        <v>-38.28703520000001</v>
+        <v>-39.20107680000001</v>
       </c>
       <c r="O99">
-        <v>-6.508795984000002</v>
+        <v>-6.664183056000002</v>
       </c>
       <c r="P99">
-        <v>-31.778239216</v>
+        <v>-32.53689374400001</v>
       </c>
       <c r="Q99">
-        <v>-30.778239216</v>
+        <v>-31.53689374400001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>6.188611511363426</v>
+        <v>9.260017267045139</v>
       </c>
       <c r="T99">
-        <v>21.99937298354721</v>
+        <v>32.99905947532081</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09658869188691938</v>
+        <v>0.09560309299011406</v>
       </c>
       <c r="W99">
-        <v>0.1814049906691066</v>
+        <v>0.1816028989275851</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.568168775805408</v>
+        <v>0.562371135235965</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9555,22 +9555,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3631711862899364</v>
+        <v>0.3647211862899363</v>
       </c>
       <c r="C100">
-        <v>-57.62681670037205</v>
+        <v>-63.97205671922256</v>
       </c>
       <c r="D100">
-        <v>368.969183299628</v>
+        <v>367.1759432807774</v>
       </c>
       <c r="E100">
-        <v>182.196</v>
+        <v>186.748</v>
       </c>
       <c r="F100">
-        <v>446.096</v>
+        <v>450.648</v>
       </c>
       <c r="G100">
         <v>19.5</v>
@@ -9591,37 +9591,37 @@
         <v>50.375</v>
       </c>
       <c r="M100">
-        <v>89.57607680000001</v>
+        <v>90.4901184</v>
       </c>
       <c r="N100">
-        <v>-39.20107680000001</v>
+        <v>-40.1151184</v>
       </c>
       <c r="O100">
-        <v>-6.664183056000002</v>
+        <v>-6.819570128000001</v>
       </c>
       <c r="P100">
-        <v>-32.53689374400001</v>
+        <v>-33.295548272</v>
       </c>
       <c r="Q100">
-        <v>-31.53689374400001</v>
+        <v>-32.295548272</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>9.260017267045139</v>
+        <v>18.47423453409028</v>
       </c>
       <c r="T100">
-        <v>32.99905947532081</v>
+        <v>65.99811895064163</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09560309299011406</v>
+        <v>0.09463740518213314</v>
       </c>
       <c r="W100">
-        <v>0.1816028989275851</v>
+        <v>0.1817968090394277</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9629,91 +9629,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.562371135235965</v>
+        <v>0.5566906187184302</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3647211862899363</v>
-      </c>
-      <c r="C101">
-        <v>-63.97205671922256</v>
-      </c>
-      <c r="D101">
-        <v>367.1759432807774</v>
-      </c>
-      <c r="E101">
-        <v>186.748</v>
-      </c>
-      <c r="F101">
-        <v>450.648</v>
-      </c>
-      <c r="G101">
-        <v>19.5</v>
-      </c>
-      <c r="H101">
-        <v>191.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>51.375</v>
-      </c>
-      <c r="K101">
-        <v>1</v>
-      </c>
-      <c r="L101">
-        <v>50.375</v>
-      </c>
-      <c r="M101">
-        <v>90.4901184</v>
-      </c>
-      <c r="N101">
-        <v>-40.1151184</v>
-      </c>
-      <c r="O101">
-        <v>-6.819570128000001</v>
-      </c>
-      <c r="P101">
-        <v>-33.295548272</v>
-      </c>
-      <c r="Q101">
-        <v>-32.295548272</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>18.47423453409028</v>
-      </c>
-      <c r="T101">
-        <v>65.99811895064163</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09463740518213314</v>
-      </c>
-      <c r="W101">
-        <v>0.1817968090394277</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5566906187184302</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
